--- a/outputs/analysis_tables.xlsx
+++ b/outputs/analysis_tables.xlsx
@@ -10,7 +10,7 @@
     <sheet name="月度KPI" sheetId="1" r:id="rId1"/>
     <sheet name="半年度对比" sheetId="2" r:id="rId2"/>
     <sheet name="差评原因结构_季度" sheetId="3" r:id="rId3"/>
-    <sheet name="品质问题类型_年度" sheetId="4" r:id="rId4"/>
+    <sheet name="结果指标_年度" sheetId="4" r:id="rId4"/>
     <sheet name="因素分解_一级类目" sheetId="5" r:id="rId5"/>
     <sheet name="因素分解_单多件" sheetId="6" r:id="rId6"/>
     <sheet name="订单结构" sheetId="7" r:id="rId7"/>
@@ -18,7 +18,7 @@
     <sheet name="品类品质排行" sheetId="9" r:id="rId9"/>
     <sheet name="单件订单_重量段" sheetId="10" r:id="rId10"/>
     <sheet name="单件订单_商品图片数" sheetId="11" r:id="rId11"/>
-    <sheet name="假货投诉_品类TOP" sheetId="12" r:id="rId12"/>
+    <sheet name="假货客诉率_品类TOP" sheetId="12" r:id="rId12"/>
     <sheet name="证伪_商家入驻时长" sheetId="13" r:id="rId13"/>
     <sheet name="证伪_是否延迟签收" sheetId="14" r:id="rId14"/>
     <sheet name="证伪_首单体验与复购" sheetId="15" r:id="rId15"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="488">
   <si>
     <t>purchase_month</t>
   </si>
@@ -190,9 +190,6 @@
     <t>fulfill</t>
   </si>
   <si>
-    <t>service</t>
-  </si>
-  <si>
     <t>other</t>
   </si>
   <si>
@@ -253,10 +250,10 @@
     <t>权重2018</t>
   </si>
   <si>
-    <t>客诉率2017</t>
-  </si>
-  <si>
-    <t>客诉率2018</t>
+    <t>品质客诉率2017</t>
+  </si>
+  <si>
+    <t>品质客诉率2018</t>
   </si>
   <si>
     <t>组内贡献</t>
@@ -265,1071 +262,1074 @@
     <t>3C数码</t>
   </si>
   <si>
+    <t>钟表与潮流好物</t>
+  </si>
+  <si>
+    <t>家居家纺</t>
+  </si>
+  <si>
+    <t>母婴玩具</t>
+  </si>
+  <si>
+    <t>运动户外</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>食品酒水</t>
+  </si>
+  <si>
+    <t>家用电器</t>
+  </si>
+  <si>
+    <t>宠物</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>图书文娱</t>
+  </si>
+  <si>
+    <t>美妆个护</t>
+  </si>
+  <si>
+    <t>汽配工具</t>
+  </si>
+  <si>
+    <t>服饰鞋包</t>
+  </si>
+  <si>
+    <t>单件</t>
+  </si>
+  <si>
+    <t>多件</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>qc_ex_missing</t>
+  </si>
+  <si>
+    <t>order_share</t>
+  </si>
+  <si>
+    <t>1 单件</t>
+  </si>
+  <si>
+    <t>2 同SKU多件</t>
+  </si>
+  <si>
+    <t>3 单商家多SKU</t>
+  </si>
+  <si>
+    <t>4 多商家</t>
+  </si>
+  <si>
+    <t>seller_id</t>
+  </si>
+  <si>
+    <t>qc_defect_cnt</t>
+  </si>
+  <si>
+    <t>qc_mismatch_cnt</t>
+  </si>
+  <si>
+    <t>qc_missing_cnt</t>
+  </si>
+  <si>
+    <t>qc_fake_cnt</t>
+  </si>
+  <si>
+    <t>qc_rate_smooth</t>
+  </si>
+  <si>
+    <t>late_rate</t>
+  </si>
+  <si>
+    <t>quality_score</t>
+  </si>
+  <si>
+    <t>risk_level</t>
+  </si>
+  <si>
+    <t>score_rank</t>
+  </si>
+  <si>
+    <t>benchmark_qc_rate</t>
+  </si>
+  <si>
+    <t>benchmark_bad_rate</t>
+  </si>
+  <si>
+    <t>c60b801f2d52c7f7f91de00870882a75</t>
+  </si>
+  <si>
+    <t>88460e8ebdecbfecb5f9601833981930</t>
+  </si>
+  <si>
+    <t>2eb70248d66e0e3ef83659f71b244378</t>
+  </si>
+  <si>
+    <t>855668e0971d4dfd7bef1b6a4133b41b</t>
+  </si>
+  <si>
+    <t>bbad7e518d7af88a0897397ffdca1979</t>
+  </si>
+  <si>
+    <t>70a12e78e608ac31179aea7f8422044b</t>
+  </si>
+  <si>
+    <t>f46490624488d3ff7ce78613913a7711</t>
+  </si>
+  <si>
+    <t>5dceca129747e92ff8ef7a997dc4f8ca</t>
+  </si>
+  <si>
+    <t>99a54764c341d5dc80b4a8fac4eba3fb</t>
+  </si>
+  <si>
+    <t>b1fc4f64df5a0e8b6913ab38803c57a9</t>
+  </si>
+  <si>
+    <t>04308b1ee57b6625f47df1d56f00eedf</t>
+  </si>
+  <si>
+    <t>7c67e1448b00f6e969d365cea6b010ab</t>
+  </si>
+  <si>
+    <t>c3867b4666c7d76867627c2f7fb22e21</t>
+  </si>
+  <si>
+    <t>d2374cbcbb3ca4ab1086534108cc3ab7</t>
+  </si>
+  <si>
+    <t>213b25e6f54661939f11710a6fddb871</t>
+  </si>
+  <si>
+    <t>dd7ddc04e1b6c2c614352b383efe2d36</t>
+  </si>
+  <si>
+    <t>972d0f9cf61b499a4812cf0bfa3ad3c4</t>
+  </si>
+  <si>
+    <t>4e922959ae960d389249c378d1c939f5</t>
+  </si>
+  <si>
+    <t>3db66a856d18a9cba7c9241fc5221c50</t>
+  </si>
+  <si>
+    <t>ea566164622c6b439516ab18062c42cd</t>
+  </si>
+  <si>
+    <t>b2479f944e1b90cf8a5de1bbfde284d6</t>
+  </si>
+  <si>
+    <t>cac4c8e7b1ca6252d8f20b2fc1a2e4af</t>
+  </si>
+  <si>
+    <t>fa40cc5b934574b62717c68f3d678b6d</t>
+  </si>
+  <si>
+    <t>897060da8b9a21f655304d50fd935913</t>
+  </si>
+  <si>
+    <t>710e3548e02bc1d2831dfc4f1b5b14d4</t>
+  </si>
+  <si>
+    <t>18a349e75d307f4b4cc646a691ed4216</t>
+  </si>
+  <si>
+    <t>7ad32824caee82087b3e2e5f33b1bf32</t>
+  </si>
+  <si>
+    <t>2138ccb85b11a4ec1e37afbd1c8eda1f</t>
+  </si>
+  <si>
+    <t>1025f0e2d44d7041d6cf58b6550e0bfa</t>
+  </si>
+  <si>
+    <t>e9bc59e7b60fc3063eb2290deda4cced</t>
+  </si>
+  <si>
+    <t>966cb4760537b1404caedd472cc610a5</t>
+  </si>
+  <si>
+    <t>95f83f51203c626648c875dd41874c7f</t>
+  </si>
+  <si>
+    <t>7202e2ba20579a9bd1acb29e61fe71f6</t>
+  </si>
+  <si>
+    <t>688756f717c462a206ad854c5027a64a</t>
+  </si>
+  <si>
+    <t>17a053fcb14bd219540cbde0df490be0</t>
+  </si>
+  <si>
+    <t>7040e82f899a04d1b434b795a43b4617</t>
+  </si>
+  <si>
+    <t>1900267e848ceeba8fa32d80c1a5f5a8</t>
+  </si>
+  <si>
+    <t>0be8ff43f22e456b4e0371b2245e4d01</t>
+  </si>
+  <si>
+    <t>ea8482cd71df3c1969d7b9473ff13abc</t>
+  </si>
+  <si>
+    <t>609e1a9a6c2539919b8205cf7c4e6ff0</t>
+  </si>
+  <si>
+    <t>b76dba6c951ab00dc4edf0a1aa88037e</t>
+  </si>
+  <si>
+    <t>c9aafcd0621b2207c10e32c649cada4d</t>
+  </si>
+  <si>
+    <t>b2ba3715d723d245138f291a6fe42594</t>
+  </si>
+  <si>
+    <t>a673821011d0cec28146ea42f5ab767f</t>
+  </si>
+  <si>
+    <t>1835b56ce799e6a4dc4eddc053f04066</t>
+  </si>
+  <si>
+    <t>09f952a5f58d2285b0372551ae8f9b01</t>
+  </si>
+  <si>
+    <t>92eb0f42c21942b6552362b9b114707d</t>
+  </si>
+  <si>
+    <t>cca3071e3e9bb7d12640c9fbe2301306</t>
+  </si>
+  <si>
+    <t>522620dcb18a6b31cd7bdf73665113a9</t>
+  </si>
+  <si>
+    <t>ce7d1888639e6fb06b2749cbfdac1ff7</t>
+  </si>
+  <si>
+    <t>4c18691b6037662be2df78a765d98ab5</t>
+  </si>
+  <si>
+    <t>6973a06f484aacf400ece213dbf3d946</t>
+  </si>
+  <si>
+    <t>6b3bd31ad8fcda4b2635ec9f3ff2ecdf</t>
+  </si>
+  <si>
+    <t>17e34d8224d27a541263c4c64b11a56b</t>
+  </si>
+  <si>
+    <t>5343d0649eca2a983820bfe93fc4d17e</t>
+  </si>
+  <si>
+    <t>ff1fb4c404b2efe68b03350a8dc24122</t>
+  </si>
+  <si>
+    <t>c31eff8334d6b3047ed34bebd4d62c36</t>
+  </si>
+  <si>
+    <t>59b22a78efb79a4797979612b885db36</t>
+  </si>
+  <si>
+    <t>d91fb3b7d041e83b64a00a3edfb37e4f</t>
+  </si>
+  <si>
+    <t>db2956745b3a8e9f3785c99f34b5d25e</t>
+  </si>
+  <si>
+    <t>8648b1e89e9b349e32d3741b30ec737e</t>
+  </si>
+  <si>
+    <t>8b9d6eec4a7eb7d0f9d579ce0b38324d</t>
+  </si>
+  <si>
+    <t>6560211a19b47992c3666cc44a7e94c0</t>
+  </si>
+  <si>
+    <t>36a968b544695394e4e9d7572688598f</t>
+  </si>
+  <si>
+    <t>4a3ca9315b744ce9f8e9374361493884</t>
+  </si>
+  <si>
+    <t>16090f2ca825584b5a147ab24aa30c86</t>
+  </si>
+  <si>
+    <t>b499c00f28f4b7069ff6550af8c1348a</t>
+  </si>
+  <si>
+    <t>634964b17796e64304cadf1ad3050fb7</t>
+  </si>
+  <si>
+    <t>5656537e588803a555b8eb41f07a944b</t>
+  </si>
+  <si>
+    <t>0dd184061fb0eaa7ca37932c68ab91c5</t>
+  </si>
+  <si>
+    <t>b39d7fe263ef469605dbb32608aee0af</t>
+  </si>
+  <si>
+    <t>0b90b6df587eb83608a64ea8b390cf07</t>
+  </si>
+  <si>
+    <t>53e4c6e0f4312d4d2107a8c9cddf45cd</t>
+  </si>
+  <si>
+    <t>81f89e42267213cb94da7ddc301651da</t>
+  </si>
+  <si>
+    <t>34056b8b55c1775a22af2331670a799c</t>
+  </si>
+  <si>
+    <t>f457c46070d02cadd8a68551231220dd</t>
+  </si>
+  <si>
+    <t>f0b47fbbc6dee9aafe415a6e33051b3f</t>
+  </si>
+  <si>
+    <t>138dbe45fc62f1e244378131a6801526</t>
+  </si>
+  <si>
+    <t>620c87c171fb2a6dd6e8bb4dec959fc6</t>
+  </si>
+  <si>
+    <t>53243585a1d6dc2643021fd1853d8905</t>
+  </si>
+  <si>
+    <t>c33847515fa6305ce6feb1e818569f13</t>
+  </si>
+  <si>
+    <t>2a261b5b644fa05f4f2700eb93544f2c</t>
+  </si>
+  <si>
+    <t>ef506c96320abeedfb894c34db06f478</t>
+  </si>
+  <si>
+    <t>d1c281d3ae149232351cd8c8cc885f0d</t>
+  </si>
+  <si>
+    <t>b839e41795b7f3ad94cc2014a52f6796</t>
+  </si>
+  <si>
+    <t>1f50f920176fa81dab994f9023523100</t>
+  </si>
+  <si>
+    <t>5d0363b33554b373851fc1622e4d5f3c</t>
+  </si>
+  <si>
+    <t>ea67327e24487bdfac5fbfa37ea124df</t>
+  </si>
+  <si>
+    <t>aafe36600ce604f205b86b5084d3d767</t>
+  </si>
+  <si>
+    <t>3d8fa2f5b647373c8620330c4e077a9f</t>
+  </si>
+  <si>
+    <t>dfa0c4c6229ab200a4a1336b4d7128ff</t>
+  </si>
+  <si>
+    <t>c9c7905cffc4ef9ff9f113554423e671</t>
+  </si>
+  <si>
+    <t>5a8e7d5003a1f221f9e1d6e411de7c23</t>
+  </si>
+  <si>
+    <t>cfb1a033743668a192316f3c6d1d2671</t>
+  </si>
+  <si>
+    <t>1c68394e931a64f90ea236c5ea590300</t>
+  </si>
+  <si>
+    <t>218d46b86c1881d022bce9c68a7d4b15</t>
+  </si>
+  <si>
+    <t>7142540dd4c91e2237acb7e911c4eba2</t>
+  </si>
+  <si>
+    <t>06e5eefc71ec47ae763c5c6f8db7064f</t>
+  </si>
+  <si>
+    <t>fcb5ace8bcc92f75707dc0f01a27d269</t>
+  </si>
+  <si>
+    <t>70c27847eca8195c983ed7e798c56743</t>
+  </si>
+  <si>
+    <t>cc419e0650a3c5ba77189a1882b7556a</t>
+  </si>
+  <si>
+    <t>46dc3b2cc0980fb8ec44634e21d2718e</t>
+  </si>
+  <si>
+    <t>a3e9a2c700480d9bb01fba070ba80a0e</t>
+  </si>
+  <si>
+    <t>98dac6635aee4995d501a3972e047414</t>
+  </si>
+  <si>
+    <t>01fd077212124329bac32490e8ef80d9</t>
+  </si>
+  <si>
+    <t>4d6d651bd7684af3fffabd5f08d12e5a</t>
+  </si>
+  <si>
+    <t>45ba18c210d42734ec52c0c1c574e9ee</t>
+  </si>
+  <si>
+    <t>f7ccf836d21b2fb1de37564105216cc1</t>
+  </si>
+  <si>
+    <t>f84a00e60c73a49e7e851c9bdca3a5bb</t>
+  </si>
+  <si>
+    <t>06a2c3af7b3aee5d69171b0e14f0ee87</t>
+  </si>
+  <si>
+    <t>955fee9216a65b617aa5c0531780ce60</t>
+  </si>
+  <si>
+    <t>f3da5b2ff499efb8d4a6d371d175d7dd</t>
+  </si>
+  <si>
+    <t>fd386aa7bed2af3c7035c65506c9b4a3</t>
+  </si>
+  <si>
+    <t>2e90cb1677d35cfe24eef47d441b7c87</t>
+  </si>
+  <si>
+    <t>4869f7a5dfa277a7dca6462dcf3b52b2</t>
+  </si>
+  <si>
+    <t>d94a40fd42351c259927028d163af842</t>
+  </si>
+  <si>
+    <t>b4ffb71f0cb1b1c3d63fad021ecf93e1</t>
+  </si>
+  <si>
+    <t>2528513dd95219a6013d4d05176e391a</t>
+  </si>
+  <si>
+    <t>d673a59aac7a70d8b01e6902bf090a11</t>
+  </si>
+  <si>
+    <t>7d13fca15225358621be4086e1eb0964</t>
+  </si>
+  <si>
+    <t>95e03ca3d4146e4011985981aeb959b9</t>
+  </si>
+  <si>
+    <t>e5a38146df062edaf55c38afa99e42dc</t>
+  </si>
+  <si>
+    <t>9b013e03b2ab786505a1d3b5c0756754</t>
+  </si>
+  <si>
+    <t>9e6229250fedbe05838fef417b74e7fb</t>
+  </si>
+  <si>
+    <t>6d66611d7c44cc30ce351abc49a68421</t>
+  </si>
+  <si>
+    <t>391fc6631aebcf3004804e51b40bcf1e</t>
+  </si>
+  <si>
+    <t>8e8a7ce9f2f970dc00e2acf6f6e199f6</t>
+  </si>
+  <si>
+    <t>6860153b69cc696d5dcfe1cdaaafcf62</t>
+  </si>
+  <si>
+    <t>cbd996ad3c1b7dc71fd0e5f5df9087e2</t>
+  </si>
+  <si>
+    <t>4830e40640734fc1c52cd21127c341d4</t>
+  </si>
+  <si>
+    <t>ede0c03645598cdfc63ca8237acbe73d</t>
+  </si>
+  <si>
+    <t>c70c1b0d8ca86052f45a432a38b73958</t>
+  </si>
+  <si>
+    <t>f262cbc1c910c83959f849465454ddd3</t>
+  </si>
+  <si>
+    <t>0241d4d5d36f10f80c644447315af0bd</t>
+  </si>
+  <si>
+    <t>e5a3438891c0bfdb9394643f95273d8e</t>
+  </si>
+  <si>
+    <t>562fc2f2c2863ab7e79a9e4388a58a14</t>
+  </si>
+  <si>
+    <t>00ee68308b45bc5e2660cd833c3f81cc</t>
+  </si>
+  <si>
+    <t>58f1a6197ed863543e0136bdedb3fce2</t>
+  </si>
+  <si>
+    <t>1554a68530182680ad5c8b042c3ab563</t>
+  </si>
+  <si>
+    <t>2e1c9f22be269ef4643f826c9e650a52</t>
+  </si>
+  <si>
+    <t>382229d1e840115ffe3dbf5ff460e417</t>
+  </si>
+  <si>
+    <t>4c2b230173bb36f9b240f2b8ac11786e</t>
+  </si>
+  <si>
+    <t>f80edd2c5aaa505cc4b0a3b219abf4b8</t>
+  </si>
+  <si>
+    <t>0ed6ce5d87fd9c69eaacaeb778d67235</t>
+  </si>
+  <si>
+    <t>aba1721a889e04decc910aa13b768ef4</t>
+  </si>
+  <si>
+    <t>3ab971ce71839580d2ae5b4e40fe8044</t>
+  </si>
+  <si>
+    <t>0df3984f9dfb3d49ac6366acbd3bbb85</t>
+  </si>
+  <si>
+    <t>e333046ce6517bd8bb510291d44f0130</t>
+  </si>
+  <si>
+    <t>8d956fec2e4337affcb520f56fd8cbfd</t>
+  </si>
+  <si>
+    <t>7681ef142fd2c19048da7430856b5588</t>
+  </si>
+  <si>
+    <t>f8db351d8c4c4c22c6835c19a46f01b0</t>
+  </si>
+  <si>
+    <t>cc63f0dd2acba93ffed4fe9f8e0321fa</t>
+  </si>
+  <si>
+    <t>d98eec89afa3380e14463da2aabaea72</t>
+  </si>
+  <si>
+    <t>7ddcbb64b5bc1ef36ca8c151f6ec77df</t>
+  </si>
+  <si>
+    <t>056b4ada5bbc2c50cc7842547dda6b51</t>
+  </si>
+  <si>
+    <t>8160255418d5aaa7dbdc9f4c64ebda44</t>
+  </si>
+  <si>
+    <t>ceaec5548eefc6e23e6607c5435102e7</t>
+  </si>
+  <si>
+    <t>beadbee30901a7f61d031b6b686095ad</t>
+  </si>
+  <si>
+    <t>b1a81260566c1bac3114a6d124413f27</t>
+  </si>
+  <si>
+    <t>259f7b5e6e482c230e5bfaa670b6bb8f</t>
+  </si>
+  <si>
+    <t>8a432f4e5b471f8da497d7dc517666e2</t>
+  </si>
+  <si>
+    <t>8581055ce74af1daba164fdbd55a40de</t>
+  </si>
+  <si>
+    <t>a416b6a846a11724393025641d4edd5e</t>
+  </si>
+  <si>
+    <t>c826c40d7b19f62a09e2d7c5e7295ee2</t>
+  </si>
+  <si>
+    <t>3d871de0142ce09b7081e2b9d1733cb1</t>
+  </si>
+  <si>
+    <t>37515688008a7a40ac93e3b2e4ab203f</t>
+  </si>
+  <si>
+    <t>9c0e69c7bf2619675bbadf47b43f655a</t>
+  </si>
+  <si>
+    <t>65febd49fd28ec955651299159b1f527</t>
+  </si>
+  <si>
+    <t>01fdefa7697d26ad920e9e0346d4bd1b</t>
+  </si>
+  <si>
+    <t>240b9776d844d37535668549a396af32</t>
+  </si>
+  <si>
+    <t>5f3ae9136c875522250f8184f253413a</t>
+  </si>
+  <si>
+    <t>d6b1ce66b035a475f00c017792ff9769</t>
+  </si>
+  <si>
+    <t>0691148aee60ca47977c187804f935ae</t>
+  </si>
+  <si>
+    <t>640e21a7d01df7614a3b4923e990d40c</t>
+  </si>
+  <si>
+    <t>709e16e2b25c7474d980076c6bfc4806</t>
+  </si>
+  <si>
+    <t>951e8cef368f09bb3f3d03c00ca4702c</t>
+  </si>
+  <si>
+    <t>1da3aeb70d7989d1e6d9b0e887f97c23</t>
+  </si>
+  <si>
+    <t>79ebd9a61bac3eaf882805ed4ecfa12a</t>
+  </si>
+  <si>
+    <t>4371b634e0efc0e22b09b52907d9d469</t>
+  </si>
+  <si>
+    <t>a420f60ff1aa9acc80d0e42959f2b313</t>
+  </si>
+  <si>
+    <t>891071be6ba827b591264c90c2ae8a63</t>
+  </si>
+  <si>
+    <t>de23c3b98a88888289c6f5cc1209054a</t>
+  </si>
+  <si>
+    <t>282f23a9769b2690c5dda22e316f9941</t>
+  </si>
+  <si>
+    <t>406822777a0b9eb5c50e442dd4cd3ec5</t>
+  </si>
+  <si>
+    <t>1d4587203296c8f4ad134dc286fa6db0</t>
+  </si>
+  <si>
+    <t>729f06993dac8e860d4f02d7088ca48a</t>
+  </si>
+  <si>
+    <t>7d76b645482be4a332374e8223836592</t>
+  </si>
+  <si>
+    <t>da8622b14eb17ae2831f4ac5b9dab84a</t>
+  </si>
+  <si>
+    <t>2a84855fd20af891be03bc5924d2b453</t>
+  </si>
+  <si>
+    <t>1c129092bf23f28a5930387c980c0dfc</t>
+  </si>
+  <si>
+    <t>fa1c13f2614d7b5c4749cbc52fecda94</t>
+  </si>
+  <si>
+    <t>612170e34b97004b3ba37eae81836b4c</t>
+  </si>
+  <si>
+    <t>ececbfcff9804a2d6b40f589df8eef2b</t>
+  </si>
+  <si>
+    <t>54a1852d1b8f10312c55e906355666ee</t>
+  </si>
+  <si>
+    <t>7178f9f4dd81dcef02f62acdf8151e01</t>
+  </si>
+  <si>
+    <t>23c38debaffe4a25a30fdbd9b586a13f</t>
+  </si>
+  <si>
+    <t>6b243f80ed07b10f0e8aa0f21a205f3c</t>
+  </si>
+  <si>
+    <t>8a130737016f838139d31878787a39c9</t>
+  </si>
+  <si>
+    <t>72c5da29406b4234927b81855e7b64f6</t>
+  </si>
+  <si>
+    <t>8f2ce03f928b567e3d56181ae20ae952</t>
+  </si>
+  <si>
+    <t>17ca9b9e9b9ef8fdb529001b49ebb50f</t>
+  </si>
+  <si>
+    <t>643214e62b870443ccbe55ab29a4dccf</t>
+  </si>
+  <si>
+    <t>f7720c4fa8e3aba4546301ab80ea1f1b</t>
+  </si>
+  <si>
+    <t>f84fa566034f5e8e880a07ec624c56af</t>
+  </si>
+  <si>
+    <t>fe2032dab1a61af8794248c8196565c9</t>
+  </si>
+  <si>
+    <t>b6d44737c043328708f6749c2dbe50bd</t>
+  </si>
+  <si>
+    <t>6edacfd9f9074789dad6d62ba7950b9c</t>
+  </si>
+  <si>
+    <t>87142160b41353c4e5fca2360caf6f92</t>
+  </si>
+  <si>
+    <t>8ae520247981aa06bc94abddf5f46d34</t>
+  </si>
+  <si>
+    <t>080102cd0a76b09e0dcf55fcacc60e05</t>
+  </si>
+  <si>
+    <t>ccc4bbb5f32a6ab2b7066a4130f114e3</t>
+  </si>
+  <si>
+    <t>32b8764b4ef628b53608fc34011fcc13</t>
+  </si>
+  <si>
+    <t>e9779976487b77c6d4ac45f75ec7afe9</t>
+  </si>
+  <si>
+    <t>c013e57c075a06e5b5c48ee03c525719</t>
+  </si>
+  <si>
+    <t>1e8b33f18b4f7598d87f5cbee2282cc2</t>
+  </si>
+  <si>
+    <t>ef0ace09169ac090589d85746e3e036f</t>
+  </si>
+  <si>
+    <t>b18dc380845b24038cfc48006478f099</t>
+  </si>
+  <si>
+    <t>f5a590cf36251cf1162ea35bef76fe84</t>
+  </si>
+  <si>
+    <t>dbc22125167c298ef99da25668e1011f</t>
+  </si>
+  <si>
+    <t>c66dccfb3f109511246da627dd5a2498</t>
+  </si>
+  <si>
+    <t>8bb48dc19fccaa8613b6229bf7f452a2</t>
+  </si>
+  <si>
+    <t>77530e9772f57a62c906e1c21538ab82</t>
+  </si>
+  <si>
+    <t>900ba814c251a692506d7834c1218441</t>
+  </si>
+  <si>
+    <t>ba143b05f0110f0dc71ad71b4466ce92</t>
+  </si>
+  <si>
+    <t>e8b4225284fbb02d16f200513f1f395d</t>
+  </si>
+  <si>
+    <t>33a17d60c64393351ebf1ef860f4e0f2</t>
+  </si>
+  <si>
+    <t>116ccb1a1604bc88e4d234a8c23f33de</t>
+  </si>
+  <si>
+    <t>537eb890efff034a88679788b647c564</t>
+  </si>
+  <si>
+    <t>128639473a139ac0f3e5f5ade55873a5</t>
+  </si>
+  <si>
+    <t>7e1fb0a3ebfb01ffb3a7dae98bf3238d</t>
+  </si>
+  <si>
+    <t>cc5a78bbad32776dc4e3af205218368c</t>
+  </si>
+  <si>
+    <t>7a67c85e85bb2ce8582c35f2203ad736</t>
+  </si>
+  <si>
+    <t>530ec6109d11eaaf87999465c6afee01</t>
+  </si>
+  <si>
+    <t>850f4f8af5ea87287ac68de36e29107f</t>
+  </si>
+  <si>
+    <t>7d456afc660226829370f3173d14520c</t>
+  </si>
+  <si>
+    <t>c8b0e2b0a7095e5d8219575d5e7e1181</t>
+  </si>
+  <si>
+    <t>8b321bb669392f5163d04c59e235e066</t>
+  </si>
+  <si>
+    <t>7e3f87d16fb353f408d467e74fbd8014</t>
+  </si>
+  <si>
+    <t>31561f325664a8a7aba4c8d0c3a9b3db</t>
+  </si>
+  <si>
+    <t>669ae81880e08f269a64487cfb287169</t>
+  </si>
+  <si>
+    <t>edb1ef5e36e0c8cd84eb3c9b003e486d</t>
+  </si>
+  <si>
+    <t>b561927807645834b59ef0d16ba55a24</t>
+  </si>
+  <si>
+    <t>2c9e548be18521d1c43cde1c582c6de8</t>
+  </si>
+  <si>
+    <t>9f505651f4a6abe901a56cdc21508025</t>
+  </si>
+  <si>
+    <t>527801b552d0077ffd170872eb49683b</t>
+  </si>
+  <si>
+    <t>02f623a8eb246f3c5f7c2f96462654e6</t>
+  </si>
+  <si>
+    <t>c3cfdc648177fdbbbb35635a37472c53</t>
+  </si>
+  <si>
+    <t>f214d28e8d8e3ef068748498ccc2f813</t>
+  </si>
+  <si>
+    <t>f7ba60f8c3f99e7ee4042fdef03b70c4</t>
+  </si>
+  <si>
+    <t>85d9eb9ddc5d00ca9336a2219c97bb13</t>
+  </si>
+  <si>
+    <t>de722cd6dad950a92b7d4f82673f8833</t>
+  </si>
+  <si>
+    <t>715bbd5ba4e6b74cb0d2f29eb45058b0</t>
+  </si>
+  <si>
+    <t>d13e50eaa47b4cbe9eb81465865d8cfc</t>
+  </si>
+  <si>
+    <t>d9a84e1403de8da0c3aa531d6d108ba6</t>
+  </si>
+  <si>
+    <t>6a8b085f816a1f75f92dbac6eb545f8f</t>
+  </si>
+  <si>
+    <t>ff063b022a9a0aab91bad2c9088760b7</t>
+  </si>
+  <si>
+    <t>0bae85eb84b9fb3bd773911e89288d54</t>
+  </si>
+  <si>
+    <t>d57e18d5f73c7ccb7f7339b61166898d</t>
+  </si>
+  <si>
+    <t>42b729f859728f5079499127a9c2ef37</t>
+  </si>
+  <si>
+    <t>5cf13accae3222c70a9cac40818ae839</t>
+  </si>
+  <si>
+    <t>70eea00b476a314817cefde4aad4f89a</t>
+  </si>
+  <si>
+    <t>e59aa562b9f8076dd550fcddf0e73491</t>
+  </si>
+  <si>
+    <t>66922902710d126a0e7d26b0e3805106</t>
+  </si>
+  <si>
+    <t>0ea22c1cfbdc755f86b9b54b39c16043</t>
+  </si>
+  <si>
+    <t>dee656f0f566ed1aa85bd137c943f08f</t>
+  </si>
+  <si>
+    <t>33a6f4b1e7cdc205511e76ba1b6e0186</t>
+  </si>
+  <si>
+    <t>289cdb325fb7e7f891c38608bf9e0962</t>
+  </si>
+  <si>
+    <t>7299e27ed73d2ad986de7f7c77d919fa</t>
+  </si>
+  <si>
+    <t>acce39e832338debb07b02385cde5967</t>
+  </si>
+  <si>
+    <t>1bb2bdb95f4841f1bba2c0d2cd83d3c9</t>
+  </si>
+  <si>
+    <t>12b9676b00f60f3b700e83af21824c0e</t>
+  </si>
+  <si>
+    <t>cab85505710c7cb9b720bceb52b01cee</t>
+  </si>
+  <si>
+    <t>670c26e0f1bf8d0576271d5cfaec6d2b</t>
+  </si>
+  <si>
+    <t>a3a38f4affed601eb87a97788c949667</t>
+  </si>
+  <si>
+    <t>c003204e1ab016dfa150abc119207b24</t>
+  </si>
+  <si>
+    <t>08633c14ef2db992c11f840f04fad4cd</t>
+  </si>
+  <si>
+    <t>7f7b8245c336066a1f9933c359f11d77</t>
+  </si>
+  <si>
+    <t>750303a20e9c56b2a6bc45cdce0b897d</t>
+  </si>
+  <si>
+    <t>4b9750c8ad28220fe6702d4ecb7c898f</t>
+  </si>
+  <si>
+    <t>e882b2a25a10b9c057cc49695f222c19</t>
+  </si>
+  <si>
+    <t>1b4c3a6f53068f0b6944d2d005c9fc89</t>
+  </si>
+  <si>
+    <t>d650b663c3b5f6fb392b6326366efa9a</t>
+  </si>
+  <si>
+    <t>080199a181c46c657dc5aa235411be3b</t>
+  </si>
+  <si>
+    <t>ba90964cff9b9e0e6f32b23b82465f7b</t>
+  </si>
+  <si>
+    <t>a5cba26a62b8b4d0145b68b841e62e7f</t>
+  </si>
+  <si>
+    <t>b410bdd36d5db7a65dcd42b7ead933b8</t>
+  </si>
+  <si>
+    <t>dbd66278cbfe1aa1000f90a217ca4695</t>
+  </si>
+  <si>
+    <t>a1043bafd471dff536d0c462352beb48</t>
+  </si>
+  <si>
+    <t>18e694e0e48ed6f7aa3f24aade5fd697</t>
+  </si>
+  <si>
+    <t>9d4db00d65d7760644ac0c14edb5fd86</t>
+  </si>
+  <si>
+    <t>d9bd94811c3338dceb4181f3dbc0c73e</t>
+  </si>
+  <si>
+    <t>d921b68bf747894be13a97ae52b0f386</t>
+  </si>
+  <si>
+    <t>d566c37fa119d5e66c4e9052e83ee4ea</t>
+  </si>
+  <si>
+    <t>d23019c84ffae2d5ef2270367b8605fc</t>
+  </si>
+  <si>
+    <t>2ff97219cb8622eaf3cd89b7d9c09824</t>
+  </si>
+  <si>
+    <t>594f9aaa48e5bf431f011ddc5669b0d5</t>
+  </si>
+  <si>
+    <t>516e7738bd8f735ac19a010ee5450d8d</t>
+  </si>
+  <si>
+    <t>7ea5bfa6c340f58f8e71fc1f0412b0d6</t>
+  </si>
+  <si>
+    <t>6b90f847357d8981edd79a1eb1bf0acb</t>
+  </si>
+  <si>
+    <t>高风险</t>
+  </si>
+  <si>
+    <t>需关注</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>category_l1</t>
+  </si>
+  <si>
+    <t>category_cn</t>
+  </si>
+  <si>
+    <t>review_cnt</t>
+  </si>
+  <si>
+    <t>bad_cnt</t>
+  </si>
+  <si>
+    <t>late_cnt</t>
+  </si>
+  <si>
+    <t>qc_share</t>
+  </si>
+  <si>
+    <t>qc_rate_rank</t>
+  </si>
+  <si>
+    <t>办公家具</t>
+  </si>
+  <si>
+    <t>家装建材</t>
+  </si>
+  <si>
+    <t>未知品类</t>
+  </si>
+  <si>
+    <t>居家舒适</t>
+  </si>
+  <si>
+    <t>手机通讯</t>
+  </si>
+  <si>
+    <t>影音设备</t>
+  </si>
+  <si>
+    <t>客厅家具</t>
+  </si>
+  <si>
+    <t>家具软装</t>
+  </si>
+  <si>
+    <t>电脑配件</t>
+  </si>
+  <si>
+    <t>床品布艺卫浴</t>
+  </si>
+  <si>
+    <t>小家电</t>
+  </si>
+  <si>
     <t>钟表礼品</t>
   </si>
   <si>
-    <t>家居家纺</t>
-  </si>
-  <si>
-    <t>母婴玩具</t>
-  </si>
-  <si>
-    <t>运动户外</t>
-  </si>
-  <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>食品酒水</t>
-  </si>
-  <si>
-    <t>家用电器</t>
-  </si>
-  <si>
-    <t>宠物</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>图书文娱</t>
-  </si>
-  <si>
-    <t>美妆个护</t>
-  </si>
-  <si>
-    <t>汽配工具</t>
-  </si>
-  <si>
-    <t>服饰鞋包</t>
-  </si>
-  <si>
-    <t>单件</t>
-  </si>
-  <si>
-    <t>多件</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>qc_ex_missing</t>
-  </si>
-  <si>
-    <t>order_share</t>
-  </si>
-  <si>
-    <t>1 单件</t>
-  </si>
-  <si>
-    <t>2 同SKU多件</t>
-  </si>
-  <si>
-    <t>3 单商家多SKU</t>
-  </si>
-  <si>
-    <t>4 多商家</t>
-  </si>
-  <si>
-    <t>seller_id</t>
-  </si>
-  <si>
-    <t>qc_defect_cnt</t>
-  </si>
-  <si>
-    <t>qc_mismatch_cnt</t>
-  </si>
-  <si>
-    <t>qc_missing_cnt</t>
-  </si>
-  <si>
-    <t>qc_fake_cnt</t>
-  </si>
-  <si>
-    <t>qc_rate_smooth</t>
-  </si>
-  <si>
-    <t>late_rate</t>
-  </si>
-  <si>
-    <t>quality_score</t>
-  </si>
-  <si>
-    <t>risk_level</t>
-  </si>
-  <si>
-    <t>score_rank</t>
-  </si>
-  <si>
-    <t>platform_qc_rate</t>
-  </si>
-  <si>
-    <t>platform_bad_rate</t>
-  </si>
-  <si>
-    <t>c60b801f2d52c7f7f91de00870882a75</t>
-  </si>
-  <si>
-    <t>88460e8ebdecbfecb5f9601833981930</t>
-  </si>
-  <si>
-    <t>2eb70248d66e0e3ef83659f71b244378</t>
-  </si>
-  <si>
-    <t>855668e0971d4dfd7bef1b6a4133b41b</t>
-  </si>
-  <si>
-    <t>bbad7e518d7af88a0897397ffdca1979</t>
-  </si>
-  <si>
-    <t>70a12e78e608ac31179aea7f8422044b</t>
-  </si>
-  <si>
-    <t>f46490624488d3ff7ce78613913a7711</t>
-  </si>
-  <si>
-    <t>5dceca129747e92ff8ef7a997dc4f8ca</t>
-  </si>
-  <si>
-    <t>99a54764c341d5dc80b4a8fac4eba3fb</t>
-  </si>
-  <si>
-    <t>b1fc4f64df5a0e8b6913ab38803c57a9</t>
-  </si>
-  <si>
-    <t>04308b1ee57b6625f47df1d56f00eedf</t>
-  </si>
-  <si>
-    <t>7c67e1448b00f6e969d365cea6b010ab</t>
-  </si>
-  <si>
-    <t>c3867b4666c7d76867627c2f7fb22e21</t>
-  </si>
-  <si>
-    <t>d2374cbcbb3ca4ab1086534108cc3ab7</t>
-  </si>
-  <si>
-    <t>213b25e6f54661939f11710a6fddb871</t>
-  </si>
-  <si>
-    <t>dd7ddc04e1b6c2c614352b383efe2d36</t>
-  </si>
-  <si>
-    <t>972d0f9cf61b499a4812cf0bfa3ad3c4</t>
-  </si>
-  <si>
-    <t>4e922959ae960d389249c378d1c939f5</t>
-  </si>
-  <si>
-    <t>3db66a856d18a9cba7c9241fc5221c50</t>
-  </si>
-  <si>
-    <t>ea566164622c6b439516ab18062c42cd</t>
-  </si>
-  <si>
-    <t>b2479f944e1b90cf8a5de1bbfde284d6</t>
-  </si>
-  <si>
-    <t>cac4c8e7b1ca6252d8f20b2fc1a2e4af</t>
-  </si>
-  <si>
-    <t>fa40cc5b934574b62717c68f3d678b6d</t>
-  </si>
-  <si>
-    <t>897060da8b9a21f655304d50fd935913</t>
-  </si>
-  <si>
-    <t>710e3548e02bc1d2831dfc4f1b5b14d4</t>
-  </si>
-  <si>
-    <t>18a349e75d307f4b4cc646a691ed4216</t>
-  </si>
-  <si>
-    <t>7ad32824caee82087b3e2e5f33b1bf32</t>
-  </si>
-  <si>
-    <t>2138ccb85b11a4ec1e37afbd1c8eda1f</t>
-  </si>
-  <si>
-    <t>1025f0e2d44d7041d6cf58b6550e0bfa</t>
-  </si>
-  <si>
-    <t>e9bc59e7b60fc3063eb2290deda4cced</t>
-  </si>
-  <si>
-    <t>966cb4760537b1404caedd472cc610a5</t>
-  </si>
-  <si>
-    <t>95f83f51203c626648c875dd41874c7f</t>
-  </si>
-  <si>
-    <t>7202e2ba20579a9bd1acb29e61fe71f6</t>
-  </si>
-  <si>
-    <t>688756f717c462a206ad854c5027a64a</t>
-  </si>
-  <si>
-    <t>17a053fcb14bd219540cbde0df490be0</t>
-  </si>
-  <si>
-    <t>7040e82f899a04d1b434b795a43b4617</t>
-  </si>
-  <si>
-    <t>1900267e848ceeba8fa32d80c1a5f5a8</t>
-  </si>
-  <si>
-    <t>0be8ff43f22e456b4e0371b2245e4d01</t>
-  </si>
-  <si>
-    <t>ea8482cd71df3c1969d7b9473ff13abc</t>
-  </si>
-  <si>
-    <t>609e1a9a6c2539919b8205cf7c4e6ff0</t>
-  </si>
-  <si>
-    <t>b76dba6c951ab00dc4edf0a1aa88037e</t>
-  </si>
-  <si>
-    <t>c9aafcd0621b2207c10e32c649cada4d</t>
-  </si>
-  <si>
-    <t>b2ba3715d723d245138f291a6fe42594</t>
-  </si>
-  <si>
-    <t>a673821011d0cec28146ea42f5ab767f</t>
-  </si>
-  <si>
-    <t>1835b56ce799e6a4dc4eddc053f04066</t>
-  </si>
-  <si>
-    <t>09f952a5f58d2285b0372551ae8f9b01</t>
-  </si>
-  <si>
-    <t>92eb0f42c21942b6552362b9b114707d</t>
-  </si>
-  <si>
-    <t>cca3071e3e9bb7d12640c9fbe2301306</t>
-  </si>
-  <si>
-    <t>522620dcb18a6b31cd7bdf73665113a9</t>
-  </si>
-  <si>
-    <t>ce7d1888639e6fb06b2749cbfdac1ff7</t>
-  </si>
-  <si>
-    <t>4c18691b6037662be2df78a765d98ab5</t>
-  </si>
-  <si>
-    <t>6973a06f484aacf400ece213dbf3d946</t>
-  </si>
-  <si>
-    <t>6b3bd31ad8fcda4b2635ec9f3ff2ecdf</t>
-  </si>
-  <si>
-    <t>17e34d8224d27a541263c4c64b11a56b</t>
-  </si>
-  <si>
-    <t>5343d0649eca2a983820bfe93fc4d17e</t>
-  </si>
-  <si>
-    <t>ff1fb4c404b2efe68b03350a8dc24122</t>
-  </si>
-  <si>
-    <t>c31eff8334d6b3047ed34bebd4d62c36</t>
-  </si>
-  <si>
-    <t>59b22a78efb79a4797979612b885db36</t>
-  </si>
-  <si>
-    <t>d91fb3b7d041e83b64a00a3edfb37e4f</t>
-  </si>
-  <si>
-    <t>db2956745b3a8e9f3785c99f34b5d25e</t>
-  </si>
-  <si>
-    <t>8648b1e89e9b349e32d3741b30ec737e</t>
-  </si>
-  <si>
-    <t>8b9d6eec4a7eb7d0f9d579ce0b38324d</t>
-  </si>
-  <si>
-    <t>6560211a19b47992c3666cc44a7e94c0</t>
-  </si>
-  <si>
-    <t>36a968b544695394e4e9d7572688598f</t>
-  </si>
-  <si>
-    <t>4a3ca9315b744ce9f8e9374361493884</t>
-  </si>
-  <si>
-    <t>16090f2ca825584b5a147ab24aa30c86</t>
-  </si>
-  <si>
-    <t>b499c00f28f4b7069ff6550af8c1348a</t>
-  </si>
-  <si>
-    <t>634964b17796e64304cadf1ad3050fb7</t>
-  </si>
-  <si>
-    <t>5656537e588803a555b8eb41f07a944b</t>
-  </si>
-  <si>
-    <t>0dd184061fb0eaa7ca37932c68ab91c5</t>
-  </si>
-  <si>
-    <t>b39d7fe263ef469605dbb32608aee0af</t>
-  </si>
-  <si>
-    <t>0b90b6df587eb83608a64ea8b390cf07</t>
-  </si>
-  <si>
-    <t>53e4c6e0f4312d4d2107a8c9cddf45cd</t>
-  </si>
-  <si>
-    <t>81f89e42267213cb94da7ddc301651da</t>
-  </si>
-  <si>
-    <t>34056b8b55c1775a22af2331670a799c</t>
-  </si>
-  <si>
-    <t>f457c46070d02cadd8a68551231220dd</t>
-  </si>
-  <si>
-    <t>f0b47fbbc6dee9aafe415a6e33051b3f</t>
-  </si>
-  <si>
-    <t>138dbe45fc62f1e244378131a6801526</t>
-  </si>
-  <si>
-    <t>620c87c171fb2a6dd6e8bb4dec959fc6</t>
-  </si>
-  <si>
-    <t>53243585a1d6dc2643021fd1853d8905</t>
-  </si>
-  <si>
-    <t>c33847515fa6305ce6feb1e818569f13</t>
-  </si>
-  <si>
-    <t>2a261b5b644fa05f4f2700eb93544f2c</t>
-  </si>
-  <si>
-    <t>ef506c96320abeedfb894c34db06f478</t>
-  </si>
-  <si>
-    <t>d1c281d3ae149232351cd8c8cc885f0d</t>
-  </si>
-  <si>
-    <t>b839e41795b7f3ad94cc2014a52f6796</t>
-  </si>
-  <si>
-    <t>1f50f920176fa81dab994f9023523100</t>
-  </si>
-  <si>
-    <t>5d0363b33554b373851fc1622e4d5f3c</t>
-  </si>
-  <si>
-    <t>ea67327e24487bdfac5fbfa37ea124df</t>
-  </si>
-  <si>
-    <t>aafe36600ce604f205b86b5084d3d767</t>
-  </si>
-  <si>
-    <t>3d8fa2f5b647373c8620330c4e077a9f</t>
-  </si>
-  <si>
-    <t>dfa0c4c6229ab200a4a1336b4d7128ff</t>
-  </si>
-  <si>
-    <t>c9c7905cffc4ef9ff9f113554423e671</t>
-  </si>
-  <si>
-    <t>5a8e7d5003a1f221f9e1d6e411de7c23</t>
-  </si>
-  <si>
-    <t>cfb1a033743668a192316f3c6d1d2671</t>
-  </si>
-  <si>
-    <t>1c68394e931a64f90ea236c5ea590300</t>
-  </si>
-  <si>
-    <t>218d46b86c1881d022bce9c68a7d4b15</t>
-  </si>
-  <si>
-    <t>7142540dd4c91e2237acb7e911c4eba2</t>
-  </si>
-  <si>
-    <t>06e5eefc71ec47ae763c5c6f8db7064f</t>
-  </si>
-  <si>
-    <t>fcb5ace8bcc92f75707dc0f01a27d269</t>
-  </si>
-  <si>
-    <t>70c27847eca8195c983ed7e798c56743</t>
-  </si>
-  <si>
-    <t>cc419e0650a3c5ba77189a1882b7556a</t>
-  </si>
-  <si>
-    <t>46dc3b2cc0980fb8ec44634e21d2718e</t>
-  </si>
-  <si>
-    <t>a3e9a2c700480d9bb01fba070ba80a0e</t>
-  </si>
-  <si>
-    <t>98dac6635aee4995d501a3972e047414</t>
-  </si>
-  <si>
-    <t>01fd077212124329bac32490e8ef80d9</t>
-  </si>
-  <si>
-    <t>4d6d651bd7684af3fffabd5f08d12e5a</t>
-  </si>
-  <si>
-    <t>45ba18c210d42734ec52c0c1c574e9ee</t>
-  </si>
-  <si>
-    <t>f7ccf836d21b2fb1de37564105216cc1</t>
-  </si>
-  <si>
-    <t>f84a00e60c73a49e7e851c9bdca3a5bb</t>
-  </si>
-  <si>
-    <t>06a2c3af7b3aee5d69171b0e14f0ee87</t>
-  </si>
-  <si>
-    <t>955fee9216a65b617aa5c0531780ce60</t>
-  </si>
-  <si>
-    <t>f3da5b2ff499efb8d4a6d371d175d7dd</t>
-  </si>
-  <si>
-    <t>fd386aa7bed2af3c7035c65506c9b4a3</t>
-  </si>
-  <si>
-    <t>2e90cb1677d35cfe24eef47d441b7c87</t>
-  </si>
-  <si>
-    <t>4869f7a5dfa277a7dca6462dcf3b52b2</t>
-  </si>
-  <si>
-    <t>d94a40fd42351c259927028d163af842</t>
-  </si>
-  <si>
-    <t>b4ffb71f0cb1b1c3d63fad021ecf93e1</t>
-  </si>
-  <si>
-    <t>2528513dd95219a6013d4d05176e391a</t>
-  </si>
-  <si>
-    <t>d673a59aac7a70d8b01e6902bf090a11</t>
-  </si>
-  <si>
-    <t>7d13fca15225358621be4086e1eb0964</t>
-  </si>
-  <si>
-    <t>95e03ca3d4146e4011985981aeb959b9</t>
-  </si>
-  <si>
-    <t>e5a38146df062edaf55c38afa99e42dc</t>
-  </si>
-  <si>
-    <t>9b013e03b2ab786505a1d3b5c0756754</t>
-  </si>
-  <si>
-    <t>9e6229250fedbe05838fef417b74e7fb</t>
-  </si>
-  <si>
-    <t>6d66611d7c44cc30ce351abc49a68421</t>
-  </si>
-  <si>
-    <t>391fc6631aebcf3004804e51b40bcf1e</t>
-  </si>
-  <si>
-    <t>8e8a7ce9f2f970dc00e2acf6f6e199f6</t>
-  </si>
-  <si>
-    <t>6860153b69cc696d5dcfe1cdaaafcf62</t>
-  </si>
-  <si>
-    <t>cbd996ad3c1b7dc71fd0e5f5df9087e2</t>
-  </si>
-  <si>
-    <t>4830e40640734fc1c52cd21127c341d4</t>
-  </si>
-  <si>
-    <t>ede0c03645598cdfc63ca8237acbe73d</t>
-  </si>
-  <si>
-    <t>c70c1b0d8ca86052f45a432a38b73958</t>
-  </si>
-  <si>
-    <t>f262cbc1c910c83959f849465454ddd3</t>
-  </si>
-  <si>
-    <t>0241d4d5d36f10f80c644447315af0bd</t>
-  </si>
-  <si>
-    <t>e5a3438891c0bfdb9394643f95273d8e</t>
-  </si>
-  <si>
-    <t>562fc2f2c2863ab7e79a9e4388a58a14</t>
-  </si>
-  <si>
-    <t>00ee68308b45bc5e2660cd833c3f81cc</t>
-  </si>
-  <si>
-    <t>58f1a6197ed863543e0136bdedb3fce2</t>
-  </si>
-  <si>
-    <t>1554a68530182680ad5c8b042c3ab563</t>
-  </si>
-  <si>
-    <t>2e1c9f22be269ef4643f826c9e650a52</t>
-  </si>
-  <si>
-    <t>382229d1e840115ffe3dbf5ff460e417</t>
-  </si>
-  <si>
-    <t>4c2b230173bb36f9b240f2b8ac11786e</t>
-  </si>
-  <si>
-    <t>f80edd2c5aaa505cc4b0a3b219abf4b8</t>
-  </si>
-  <si>
-    <t>0ed6ce5d87fd9c69eaacaeb778d67235</t>
-  </si>
-  <si>
-    <t>aba1721a889e04decc910aa13b768ef4</t>
-  </si>
-  <si>
-    <t>3ab971ce71839580d2ae5b4e40fe8044</t>
-  </si>
-  <si>
-    <t>0df3984f9dfb3d49ac6366acbd3bbb85</t>
-  </si>
-  <si>
-    <t>e333046ce6517bd8bb510291d44f0130</t>
-  </si>
-  <si>
-    <t>8d956fec2e4337affcb520f56fd8cbfd</t>
-  </si>
-  <si>
-    <t>7681ef142fd2c19048da7430856b5588</t>
-  </si>
-  <si>
-    <t>f8db351d8c4c4c22c6835c19a46f01b0</t>
-  </si>
-  <si>
-    <t>cc63f0dd2acba93ffed4fe9f8e0321fa</t>
-  </si>
-  <si>
-    <t>d98eec89afa3380e14463da2aabaea72</t>
-  </si>
-  <si>
-    <t>7ddcbb64b5bc1ef36ca8c151f6ec77df</t>
-  </si>
-  <si>
-    <t>056b4ada5bbc2c50cc7842547dda6b51</t>
-  </si>
-  <si>
-    <t>8160255418d5aaa7dbdc9f4c64ebda44</t>
-  </si>
-  <si>
-    <t>ceaec5548eefc6e23e6607c5435102e7</t>
-  </si>
-  <si>
-    <t>beadbee30901a7f61d031b6b686095ad</t>
-  </si>
-  <si>
-    <t>b1a81260566c1bac3114a6d124413f27</t>
-  </si>
-  <si>
-    <t>259f7b5e6e482c230e5bfaa670b6bb8f</t>
-  </si>
-  <si>
-    <t>8a432f4e5b471f8da497d7dc517666e2</t>
-  </si>
-  <si>
-    <t>8581055ce74af1daba164fdbd55a40de</t>
-  </si>
-  <si>
-    <t>a416b6a846a11724393025641d4edd5e</t>
-  </si>
-  <si>
-    <t>c826c40d7b19f62a09e2d7c5e7295ee2</t>
-  </si>
-  <si>
-    <t>3d871de0142ce09b7081e2b9d1733cb1</t>
-  </si>
-  <si>
-    <t>37515688008a7a40ac93e3b2e4ab203f</t>
-  </si>
-  <si>
-    <t>9c0e69c7bf2619675bbadf47b43f655a</t>
-  </si>
-  <si>
-    <t>65febd49fd28ec955651299159b1f527</t>
-  </si>
-  <si>
-    <t>01fdefa7697d26ad920e9e0346d4bd1b</t>
-  </si>
-  <si>
-    <t>240b9776d844d37535668549a396af32</t>
-  </si>
-  <si>
-    <t>5f3ae9136c875522250f8184f253413a</t>
-  </si>
-  <si>
-    <t>d6b1ce66b035a475f00c017792ff9769</t>
-  </si>
-  <si>
-    <t>0691148aee60ca47977c187804f935ae</t>
-  </si>
-  <si>
-    <t>640e21a7d01df7614a3b4923e990d40c</t>
-  </si>
-  <si>
-    <t>709e16e2b25c7474d980076c6bfc4806</t>
-  </si>
-  <si>
-    <t>951e8cef368f09bb3f3d03c00ca4702c</t>
-  </si>
-  <si>
-    <t>1da3aeb70d7989d1e6d9b0e887f97c23</t>
-  </si>
-  <si>
-    <t>79ebd9a61bac3eaf882805ed4ecfa12a</t>
-  </si>
-  <si>
-    <t>4371b634e0efc0e22b09b52907d9d469</t>
-  </si>
-  <si>
-    <t>a420f60ff1aa9acc80d0e42959f2b313</t>
-  </si>
-  <si>
-    <t>891071be6ba827b591264c90c2ae8a63</t>
-  </si>
-  <si>
-    <t>de23c3b98a88888289c6f5cc1209054a</t>
-  </si>
-  <si>
-    <t>282f23a9769b2690c5dda22e316f9941</t>
-  </si>
-  <si>
-    <t>406822777a0b9eb5c50e442dd4cd3ec5</t>
-  </si>
-  <si>
-    <t>1d4587203296c8f4ad134dc286fa6db0</t>
-  </si>
-  <si>
-    <t>729f06993dac8e860d4f02d7088ca48a</t>
-  </si>
-  <si>
-    <t>7d76b645482be4a332374e8223836592</t>
-  </si>
-  <si>
-    <t>da8622b14eb17ae2831f4ac5b9dab84a</t>
-  </si>
-  <si>
-    <t>2a84855fd20af891be03bc5924d2b453</t>
-  </si>
-  <si>
-    <t>1c129092bf23f28a5930387c980c0dfc</t>
-  </si>
-  <si>
-    <t>fa1c13f2614d7b5c4749cbc52fecda94</t>
-  </si>
-  <si>
-    <t>612170e34b97004b3ba37eae81836b4c</t>
-  </si>
-  <si>
-    <t>ececbfcff9804a2d6b40f589df8eef2b</t>
-  </si>
-  <si>
-    <t>54a1852d1b8f10312c55e906355666ee</t>
-  </si>
-  <si>
-    <t>7178f9f4dd81dcef02f62acdf8151e01</t>
-  </si>
-  <si>
-    <t>23c38debaffe4a25a30fdbd9b586a13f</t>
-  </si>
-  <si>
-    <t>6b243f80ed07b10f0e8aa0f21a205f3c</t>
-  </si>
-  <si>
-    <t>8a130737016f838139d31878787a39c9</t>
-  </si>
-  <si>
-    <t>72c5da29406b4234927b81855e7b64f6</t>
-  </si>
-  <si>
-    <t>8f2ce03f928b567e3d56181ae20ae952</t>
-  </si>
-  <si>
-    <t>17ca9b9e9b9ef8fdb529001b49ebb50f</t>
-  </si>
-  <si>
-    <t>643214e62b870443ccbe55ab29a4dccf</t>
-  </si>
-  <si>
-    <t>f7720c4fa8e3aba4546301ab80ea1f1b</t>
-  </si>
-  <si>
-    <t>f84fa566034f5e8e880a07ec624c56af</t>
-  </si>
-  <si>
-    <t>fe2032dab1a61af8794248c8196565c9</t>
-  </si>
-  <si>
-    <t>b6d44737c043328708f6749c2dbe50bd</t>
-  </si>
-  <si>
-    <t>6edacfd9f9074789dad6d62ba7950b9c</t>
-  </si>
-  <si>
-    <t>87142160b41353c4e5fca2360caf6f92</t>
-  </si>
-  <si>
-    <t>8ae520247981aa06bc94abddf5f46d34</t>
-  </si>
-  <si>
-    <t>080102cd0a76b09e0dcf55fcacc60e05</t>
-  </si>
-  <si>
-    <t>ccc4bbb5f32a6ab2b7066a4130f114e3</t>
-  </si>
-  <si>
-    <t>32b8764b4ef628b53608fc34011fcc13</t>
-  </si>
-  <si>
-    <t>e9779976487b77c6d4ac45f75ec7afe9</t>
-  </si>
-  <si>
-    <t>c013e57c075a06e5b5c48ee03c525719</t>
-  </si>
-  <si>
-    <t>1e8b33f18b4f7598d87f5cbee2282cc2</t>
-  </si>
-  <si>
-    <t>ef0ace09169ac090589d85746e3e036f</t>
-  </si>
-  <si>
-    <t>b18dc380845b24038cfc48006478f099</t>
-  </si>
-  <si>
-    <t>f5a590cf36251cf1162ea35bef76fe84</t>
-  </si>
-  <si>
-    <t>dbc22125167c298ef99da25668e1011f</t>
-  </si>
-  <si>
-    <t>c66dccfb3f109511246da627dd5a2498</t>
-  </si>
-  <si>
-    <t>8bb48dc19fccaa8613b6229bf7f452a2</t>
-  </si>
-  <si>
-    <t>77530e9772f57a62c906e1c21538ab82</t>
-  </si>
-  <si>
-    <t>900ba814c251a692506d7834c1218441</t>
-  </si>
-  <si>
-    <t>ba143b05f0110f0dc71ad71b4466ce92</t>
-  </si>
-  <si>
-    <t>e8b4225284fbb02d16f200513f1f395d</t>
-  </si>
-  <si>
-    <t>33a17d60c64393351ebf1ef860f4e0f2</t>
-  </si>
-  <si>
-    <t>116ccb1a1604bc88e4d234a8c23f33de</t>
-  </si>
-  <si>
-    <t>537eb890efff034a88679788b647c564</t>
-  </si>
-  <si>
-    <t>128639473a139ac0f3e5f5ade55873a5</t>
-  </si>
-  <si>
-    <t>7e1fb0a3ebfb01ffb3a7dae98bf3238d</t>
-  </si>
-  <si>
-    <t>cc5a78bbad32776dc4e3af205218368c</t>
-  </si>
-  <si>
-    <t>7a67c85e85bb2ce8582c35f2203ad736</t>
-  </si>
-  <si>
-    <t>530ec6109d11eaaf87999465c6afee01</t>
-  </si>
-  <si>
-    <t>850f4f8af5ea87287ac68de36e29107f</t>
-  </si>
-  <si>
-    <t>7d456afc660226829370f3173d14520c</t>
-  </si>
-  <si>
-    <t>c8b0e2b0a7095e5d8219575d5e7e1181</t>
-  </si>
-  <si>
-    <t>8b321bb669392f5163d04c59e235e066</t>
-  </si>
-  <si>
-    <t>7e3f87d16fb353f408d467e74fbd8014</t>
-  </si>
-  <si>
-    <t>31561f325664a8a7aba4c8d0c3a9b3db</t>
-  </si>
-  <si>
-    <t>669ae81880e08f269a64487cfb287169</t>
-  </si>
-  <si>
-    <t>edb1ef5e36e0c8cd84eb3c9b003e486d</t>
-  </si>
-  <si>
-    <t>b561927807645834b59ef0d16ba55a24</t>
-  </si>
-  <si>
-    <t>2c9e548be18521d1c43cde1c582c6de8</t>
-  </si>
-  <si>
-    <t>9f505651f4a6abe901a56cdc21508025</t>
-  </si>
-  <si>
-    <t>527801b552d0077ffd170872eb49683b</t>
-  </si>
-  <si>
-    <t>02f623a8eb246f3c5f7c2f96462654e6</t>
-  </si>
-  <si>
-    <t>c3cfdc648177fdbbbb35635a37472c53</t>
-  </si>
-  <si>
-    <t>f214d28e8d8e3ef068748498ccc2f813</t>
-  </si>
-  <si>
-    <t>f7ba60f8c3f99e7ee4042fdef03b70c4</t>
-  </si>
-  <si>
-    <t>85d9eb9ddc5d00ca9336a2219c97bb13</t>
-  </si>
-  <si>
-    <t>de722cd6dad950a92b7d4f82673f8833</t>
-  </si>
-  <si>
-    <t>715bbd5ba4e6b74cb0d2f29eb45058b0</t>
-  </si>
-  <si>
-    <t>d13e50eaa47b4cbe9eb81465865d8cfc</t>
-  </si>
-  <si>
-    <t>d9a84e1403de8da0c3aa531d6d108ba6</t>
-  </si>
-  <si>
-    <t>6a8b085f816a1f75f92dbac6eb545f8f</t>
-  </si>
-  <si>
-    <t>ff063b022a9a0aab91bad2c9088760b7</t>
-  </si>
-  <si>
-    <t>0bae85eb84b9fb3bd773911e89288d54</t>
-  </si>
-  <si>
-    <t>d57e18d5f73c7ccb7f7339b61166898d</t>
-  </si>
-  <si>
-    <t>42b729f859728f5079499127a9c2ef37</t>
-  </si>
-  <si>
-    <t>5cf13accae3222c70a9cac40818ae839</t>
-  </si>
-  <si>
-    <t>70eea00b476a314817cefde4aad4f89a</t>
-  </si>
-  <si>
-    <t>e59aa562b9f8076dd550fcddf0e73491</t>
-  </si>
-  <si>
-    <t>66922902710d126a0e7d26b0e3805106</t>
-  </si>
-  <si>
-    <t>0ea22c1cfbdc755f86b9b54b39c16043</t>
-  </si>
-  <si>
-    <t>dee656f0f566ed1aa85bd137c943f08f</t>
-  </si>
-  <si>
-    <t>33a6f4b1e7cdc205511e76ba1b6e0186</t>
-  </si>
-  <si>
-    <t>289cdb325fb7e7f891c38608bf9e0962</t>
-  </si>
-  <si>
-    <t>7299e27ed73d2ad986de7f7c77d919fa</t>
-  </si>
-  <si>
-    <t>acce39e832338debb07b02385cde5967</t>
-  </si>
-  <si>
-    <t>1bb2bdb95f4841f1bba2c0d2cd83d3c9</t>
-  </si>
-  <si>
-    <t>12b9676b00f60f3b700e83af21824c0e</t>
-  </si>
-  <si>
-    <t>cab85505710c7cb9b720bceb52b01cee</t>
-  </si>
-  <si>
-    <t>670c26e0f1bf8d0576271d5cfaec6d2b</t>
-  </si>
-  <si>
-    <t>a3a38f4affed601eb87a97788c949667</t>
-  </si>
-  <si>
-    <t>c003204e1ab016dfa150abc119207b24</t>
-  </si>
-  <si>
-    <t>08633c14ef2db992c11f840f04fad4cd</t>
-  </si>
-  <si>
-    <t>7f7b8245c336066a1f9933c359f11d77</t>
-  </si>
-  <si>
-    <t>750303a20e9c56b2a6bc45cdce0b897d</t>
-  </si>
-  <si>
-    <t>4b9750c8ad28220fe6702d4ecb7c898f</t>
-  </si>
-  <si>
-    <t>e882b2a25a10b9c057cc49695f222c19</t>
-  </si>
-  <si>
-    <t>1b4c3a6f53068f0b6944d2d005c9fc89</t>
-  </si>
-  <si>
-    <t>d650b663c3b5f6fb392b6326366efa9a</t>
-  </si>
-  <si>
-    <t>080199a181c46c657dc5aa235411be3b</t>
-  </si>
-  <si>
-    <t>ba90964cff9b9e0e6f32b23b82465f7b</t>
-  </si>
-  <si>
-    <t>a5cba26a62b8b4d0145b68b841e62e7f</t>
-  </si>
-  <si>
-    <t>b410bdd36d5db7a65dcd42b7ead933b8</t>
-  </si>
-  <si>
-    <t>dbd66278cbfe1aa1000f90a217ca4695</t>
-  </si>
-  <si>
-    <t>a1043bafd471dff536d0c462352beb48</t>
-  </si>
-  <si>
-    <t>18e694e0e48ed6f7aa3f24aade5fd697</t>
-  </si>
-  <si>
-    <t>9d4db00d65d7760644ac0c14edb5fd86</t>
-  </si>
-  <si>
-    <t>d9bd94811c3338dceb4181f3dbc0c73e</t>
-  </si>
-  <si>
-    <t>d921b68bf747894be13a97ae52b0f386</t>
-  </si>
-  <si>
-    <t>d566c37fa119d5e66c4e9052e83ee4ea</t>
-  </si>
-  <si>
-    <t>d23019c84ffae2d5ef2270367b8605fc</t>
-  </si>
-  <si>
-    <t>2ff97219cb8622eaf3cd89b7d9c09824</t>
-  </si>
-  <si>
-    <t>594f9aaa48e5bf431f011ddc5669b0d5</t>
-  </si>
-  <si>
-    <t>516e7738bd8f735ac19a010ee5450d8d</t>
-  </si>
-  <si>
-    <t>7ea5bfa6c340f58f8e71fc1f0412b0d6</t>
-  </si>
-  <si>
-    <t>6b90f847357d8981edd79a1eb1bf0acb</t>
-  </si>
-  <si>
-    <t>高风险</t>
-  </si>
-  <si>
-    <t>需关注</t>
-  </si>
-  <si>
-    <t>正常</t>
-  </si>
-  <si>
-    <t>category_l1</t>
-  </si>
-  <si>
-    <t>category_cn</t>
-  </si>
-  <si>
-    <t>review_cnt</t>
-  </si>
-  <si>
-    <t>bad_cnt</t>
-  </si>
-  <si>
-    <t>late_cnt</t>
-  </si>
-  <si>
-    <t>qc_share</t>
-  </si>
-  <si>
-    <t>qc_rate_rank</t>
-  </si>
-  <si>
-    <t>办公家具</t>
-  </si>
-  <si>
-    <t>家装建材</t>
-  </si>
-  <si>
-    <t>未知品类</t>
-  </si>
-  <si>
-    <t>居家舒适</t>
-  </si>
-  <si>
-    <t>手机通讯</t>
-  </si>
-  <si>
-    <t>影音设备</t>
-  </si>
-  <si>
-    <t>客厅家具</t>
-  </si>
-  <si>
-    <t>家具软装</t>
-  </si>
-  <si>
-    <t>电脑配件</t>
-  </si>
-  <si>
-    <t>床品布艺卫浴</t>
-  </si>
-  <si>
-    <t>小家电</t>
-  </si>
-  <si>
     <t>电子产品</t>
   </si>
   <si>
@@ -1444,7 +1444,7 @@
     <t>1 首单品质客诉</t>
   </si>
   <si>
-    <t>2 首单其他差评</t>
+    <t>2 首单差评（非品质）</t>
   </si>
   <si>
     <t>3 首单3-4星</t>
@@ -1480,19 +1480,19 @@
     <t>多件订单出库复核 + 分包裹提醒</t>
   </si>
   <si>
-    <t>高风险/需关注商家整改</t>
-  </si>
-  <si>
-    <t>3C数码/钟表礼品 正品与描述专项</t>
-  </si>
-  <si>
-    <t>多件订单的少件/漏发客诉减少 50%</t>
-  </si>
-  <si>
-    <t>该类商家的品质客诉减少 30%</t>
-  </si>
-  <si>
-    <t>两类目假货 + 货不对板客诉减少 30%</t>
+    <t>高风险商家和需关注商家整改</t>
+  </si>
+  <si>
+    <t>3C数码、钟表与潮流好物正品与商品描述专项</t>
+  </si>
+  <si>
+    <t>多件订单中命中少件漏发标签的品质客诉订单减少 50%</t>
+  </si>
+  <si>
+    <t>主商家为高风险商家或需关注商家的品质客诉订单减少 30%</t>
+  </si>
+  <si>
+    <t>主品类属于一级类目 3C数码、钟表与潮流好物且命中假货或货不对板标签的品质客诉订单减少 30%</t>
   </si>
 </sst>
 </file>
@@ -3387,16 +3387,16 @@
         <v>452</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
         <v>64</v>
-      </c>
-      <c r="E1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3482,16 +3482,16 @@
         <v>457</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
         <v>66</v>
-      </c>
-      <c r="E1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3577,10 +3577,10 @@
         <v>462</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
         <v>9</v>
@@ -3588,7 +3588,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B2">
         <v>1356</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B3">
         <v>6499</v>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B4">
         <v>342</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="B5">
         <v>5472</v>
@@ -3685,10 +3685,10 @@
         <v>457</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3750,16 +3750,16 @@
         <v>467</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
@@ -4045,10 +4045,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -4064,147 +4064,123 @@
       <c r="E1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>56</v>
       </c>
       <c r="B2">
         <v>172</v>
       </c>
       <c r="C2">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="E2">
-        <v>161</v>
-      </c>
-      <c r="F2">
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>283</v>
       </c>
       <c r="C3">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="D3">
-        <v>54</v>
+        <v>278</v>
       </c>
       <c r="E3">
-        <v>278</v>
-      </c>
-      <c r="F3">
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4">
         <v>407</v>
       </c>
       <c r="C4">
-        <v>318</v>
+        <v>411</v>
       </c>
       <c r="D4">
-        <v>93</v>
+        <v>308</v>
       </c>
       <c r="E4">
-        <v>308</v>
-      </c>
-      <c r="F4">
         <v>378</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5">
         <v>645</v>
       </c>
       <c r="C5">
-        <v>833</v>
+        <v>967</v>
       </c>
       <c r="D5">
-        <v>134</v>
+        <v>542</v>
       </c>
       <c r="E5">
-        <v>542</v>
-      </c>
-      <c r="F5">
         <v>778</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6">
         <v>841</v>
       </c>
       <c r="C6">
-        <v>1366</v>
+        <v>1546</v>
       </c>
       <c r="D6">
-        <v>180</v>
+        <v>691</v>
       </c>
       <c r="E6">
-        <v>691</v>
-      </c>
-      <c r="F6">
         <v>1062</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7">
         <v>814</v>
       </c>
       <c r="C7">
-        <v>567</v>
+        <v>665</v>
       </c>
       <c r="D7">
-        <v>98</v>
+        <v>399</v>
       </c>
       <c r="E7">
-        <v>399</v>
-      </c>
-      <c r="F7">
         <v>492</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8">
         <v>494</v>
       </c>
       <c r="C8">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="D8">
-        <v>55</v>
+        <v>232</v>
       </c>
       <c r="E8">
-        <v>232</v>
-      </c>
-      <c r="F8">
         <v>287</v>
       </c>
     </row>
@@ -4223,30 +4199,30 @@
         <v>44</v>
       </c>
       <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>67</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>68</v>
-      </c>
-      <c r="H1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2">
         <v>43426</v>
@@ -4308,27 +4284,27 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>74</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>75</v>
-      </c>
-      <c r="F1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>0.1476765071616083</v>
@@ -4348,7 +4324,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>0.09692350204946346</v>
@@ -4368,7 +4344,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <v>0.2560908211670428</v>
@@ -4388,7 +4364,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>0.08172523373094459</v>
@@ -4408,7 +4384,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>0.08119559710772348</v>
@@ -4428,7 +4404,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7">
         <v>0.01763920232119007</v>
@@ -4448,7 +4424,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8">
         <v>0.006240501082300925</v>
@@ -4468,7 +4444,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9">
         <v>0.01660295675401833</v>
@@ -4488,7 +4464,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10">
         <v>0.01563579422465804</v>
@@ -4508,7 +4484,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11">
         <v>0.005872058213973195</v>
@@ -4528,7 +4504,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12">
         <v>0.03341316262147101</v>
@@ -4548,7 +4524,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13">
         <v>0.1126744346704739</v>
@@ -4568,7 +4544,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14">
         <v>0.08425827845069774</v>
@@ -4588,7 +4564,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15">
         <v>0.04405195044443421</v>
@@ -4618,27 +4594,27 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>72</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>74</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>75</v>
-      </c>
-      <c r="F1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>0.8996914290977756</v>
@@ -4658,7 +4634,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3">
         <v>0.1003085709022245</v>
@@ -4688,30 +4664,30 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s">
         <v>93</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
         <v>94</v>
-      </c>
-      <c r="C1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" t="s">
-        <v>95</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2">
         <v>86598</v>
@@ -4734,7 +4710,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3">
         <v>6417</v>
@@ -4757,7 +4733,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4">
         <v>1916</v>
@@ -4780,7 +4756,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5">
         <v>1272</v>
@@ -4813,7 +4789,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -4828,22 +4804,22 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" t="s">
         <v>102</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>103</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>104</v>
-      </c>
-      <c r="I1" t="s">
-        <v>105</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L1" t="s">
         <v>11</v>
@@ -4852,30 +4828,30 @@
         <v>15</v>
       </c>
       <c r="N1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O1" t="s">
         <v>13</v>
       </c>
       <c r="P1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q1" t="s">
         <v>108</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>109</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>110</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>111</v>
-      </c>
-      <c r="T1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B2">
         <v>38</v>
@@ -4923,7 +4899,7 @@
         <v>2.3</v>
       </c>
       <c r="Q2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R2">
         <v>299</v>
@@ -4937,7 +4913,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B3">
         <v>164</v>
@@ -4985,7 +4961,7 @@
         <v>3</v>
       </c>
       <c r="Q3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R3">
         <v>298</v>
@@ -4999,7 +4975,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4">
         <v>197</v>
@@ -5047,7 +5023,7 @@
         <v>3.1</v>
       </c>
       <c r="Q4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R4">
         <v>297</v>
@@ -5061,7 +5037,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B5">
         <v>81</v>
@@ -5109,7 +5085,7 @@
         <v>3.8</v>
       </c>
       <c r="Q5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R5">
         <v>296</v>
@@ -5123,7 +5099,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B6">
         <v>33</v>
@@ -5171,7 +5147,7 @@
         <v>4.5</v>
       </c>
       <c r="Q6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R6">
         <v>295</v>
@@ -5185,7 +5161,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7">
         <v>59</v>
@@ -5233,7 +5209,7 @@
         <v>6.4</v>
       </c>
       <c r="Q7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R7">
         <v>294</v>
@@ -5247,7 +5223,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8">
         <v>83</v>
@@ -5295,7 +5271,7 @@
         <v>6.6</v>
       </c>
       <c r="Q8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R8">
         <v>293</v>
@@ -5309,7 +5285,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B9">
         <v>58</v>
@@ -5357,7 +5333,7 @@
         <v>7.6</v>
       </c>
       <c r="Q9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R9">
         <v>292</v>
@@ -5371,7 +5347,7 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10">
         <v>45</v>
@@ -5419,7 +5395,7 @@
         <v>8.1</v>
       </c>
       <c r="Q10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R10">
         <v>291</v>
@@ -5433,7 +5409,7 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B11">
         <v>45</v>
@@ -5481,7 +5457,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Q11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R11">
         <v>290</v>
@@ -5495,7 +5471,7 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12">
         <v>75</v>
@@ -5543,7 +5519,7 @@
         <v>10</v>
       </c>
       <c r="Q12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R12">
         <v>289</v>
@@ -5557,7 +5533,7 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B13">
         <v>345</v>
@@ -5605,7 +5581,7 @@
         <v>10.3</v>
       </c>
       <c r="Q13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R13">
         <v>288</v>
@@ -5619,7 +5595,7 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B14">
         <v>44</v>
@@ -5667,7 +5643,7 @@
         <v>11.4</v>
       </c>
       <c r="Q14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R14">
         <v>287</v>
@@ -5681,7 +5657,7 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B15">
         <v>170</v>
@@ -5729,7 +5705,7 @@
         <v>11.7</v>
       </c>
       <c r="Q15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R15">
         <v>286</v>
@@ -5743,7 +5719,7 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B16">
         <v>145</v>
@@ -5791,7 +5767,7 @@
         <v>13.1</v>
       </c>
       <c r="Q16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R16">
         <v>285</v>
@@ -5805,7 +5781,7 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B17">
         <v>61</v>
@@ -5853,7 +5829,7 @@
         <v>13.5</v>
       </c>
       <c r="Q17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R17">
         <v>284</v>
@@ -5867,7 +5843,7 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B18">
         <v>36</v>
@@ -5915,7 +5891,7 @@
         <v>13.9</v>
       </c>
       <c r="Q18" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R18">
         <v>283</v>
@@ -5929,7 +5905,7 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19">
         <v>98</v>
@@ -5977,7 +5953,7 @@
         <v>15.1</v>
       </c>
       <c r="Q19" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R19">
         <v>282</v>
@@ -5991,7 +5967,7 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B20">
         <v>34</v>
@@ -6039,7 +6015,7 @@
         <v>15.2</v>
       </c>
       <c r="Q20" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R20">
         <v>281</v>
@@ -6053,7 +6029,7 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B21">
         <v>39</v>
@@ -6101,7 +6077,7 @@
         <v>16.7</v>
       </c>
       <c r="Q21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R21">
         <v>280</v>
@@ -6115,7 +6091,7 @@
     </row>
     <row r="22" spans="1:20">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B22">
         <v>71</v>
@@ -6163,7 +6139,7 @@
         <v>18.6</v>
       </c>
       <c r="Q22" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R22">
         <v>279</v>
@@ -6177,7 +6153,7 @@
     </row>
     <row r="23" spans="1:20">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B23">
         <v>37</v>
@@ -6225,7 +6201,7 @@
         <v>19.1</v>
       </c>
       <c r="Q23" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R23">
         <v>278</v>
@@ -6239,7 +6215,7 @@
     </row>
     <row r="24" spans="1:20">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B24">
         <v>39</v>
@@ -6287,7 +6263,7 @@
         <v>19.3</v>
       </c>
       <c r="Q24" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R24">
         <v>277</v>
@@ -6301,7 +6277,7 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B25">
         <v>49</v>
@@ -6349,7 +6325,7 @@
         <v>19.6</v>
       </c>
       <c r="Q25" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R25">
         <v>276</v>
@@ -6363,7 +6339,7 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B26">
         <v>33</v>
@@ -6411,7 +6387,7 @@
         <v>19.7</v>
       </c>
       <c r="Q26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R26">
         <v>275</v>
@@ -6425,7 +6401,7 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B27">
         <v>92</v>
@@ -6473,7 +6449,7 @@
         <v>20.1</v>
       </c>
       <c r="Q27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R27">
         <v>274</v>
@@ -6487,7 +6463,7 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B28">
         <v>143</v>
@@ -6535,7 +6511,7 @@
         <v>20.1</v>
       </c>
       <c r="Q28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R28">
         <v>273</v>
@@ -6549,7 +6525,7 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B29">
         <v>70</v>
@@ -6597,7 +6573,7 @@
         <v>21</v>
       </c>
       <c r="Q29" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R29">
         <v>272</v>
@@ -6611,7 +6587,7 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B30">
         <v>607</v>
@@ -6659,7 +6635,7 @@
         <v>21.5</v>
       </c>
       <c r="Q30" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R30">
         <v>271</v>
@@ -6673,7 +6649,7 @@
     </row>
     <row r="31" spans="1:20">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B31">
         <v>107</v>
@@ -6721,7 +6697,7 @@
         <v>21.7</v>
       </c>
       <c r="Q31" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R31">
         <v>270</v>
@@ -6735,7 +6711,7 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B32">
         <v>75</v>
@@ -6783,7 +6759,7 @@
         <v>21.9</v>
       </c>
       <c r="Q32" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R32">
         <v>269</v>
@@ -6797,7 +6773,7 @@
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B33">
         <v>31</v>
@@ -6845,7 +6821,7 @@
         <v>22</v>
       </c>
       <c r="Q33" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R33">
         <v>268</v>
@@ -6859,7 +6835,7 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B34">
         <v>30</v>
@@ -6907,7 +6883,7 @@
         <v>22.1</v>
       </c>
       <c r="Q34" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R34">
         <v>266</v>
@@ -6921,7 +6897,7 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B35">
         <v>83</v>
@@ -6969,7 +6945,7 @@
         <v>22.1</v>
       </c>
       <c r="Q35" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R35">
         <v>267</v>
@@ -6983,7 +6959,7 @@
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B36">
         <v>72</v>
@@ -7031,7 +7007,7 @@
         <v>22.4</v>
       </c>
       <c r="Q36" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R36">
         <v>265</v>
@@ -7045,7 +7021,7 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B37">
         <v>92</v>
@@ -7093,7 +7069,7 @@
         <v>22.5</v>
       </c>
       <c r="Q37" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R37">
         <v>264</v>
@@ -7107,7 +7083,7 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B38">
         <v>181</v>
@@ -7155,7 +7131,7 @@
         <v>22.7</v>
       </c>
       <c r="Q38" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R38">
         <v>263</v>
@@ -7169,7 +7145,7 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B39">
         <v>60</v>
@@ -7217,7 +7193,7 @@
         <v>22.9</v>
       </c>
       <c r="Q39" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R39">
         <v>262</v>
@@ -7231,7 +7207,7 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40">
         <v>502</v>
@@ -7279,7 +7255,7 @@
         <v>23</v>
       </c>
       <c r="Q40" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R40">
         <v>260</v>
@@ -7293,7 +7269,7 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41">
         <v>83</v>
@@ -7341,7 +7317,7 @@
         <v>23</v>
       </c>
       <c r="Q41" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R41">
         <v>261</v>
@@ -7355,7 +7331,7 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B42">
         <v>41</v>
@@ -7403,7 +7379,7 @@
         <v>24.3</v>
       </c>
       <c r="Q42" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R42">
         <v>259</v>
@@ -7417,7 +7393,7 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43">
         <v>44</v>
@@ -7465,7 +7441,7 @@
         <v>24.3</v>
       </c>
       <c r="Q43" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R43">
         <v>258</v>
@@ -7479,7 +7455,7 @@
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B44">
         <v>61</v>
@@ -7527,7 +7503,7 @@
         <v>24.5</v>
       </c>
       <c r="Q44" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R44">
         <v>257</v>
@@ -7541,7 +7517,7 @@
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B45">
         <v>49</v>
@@ -7589,7 +7565,7 @@
         <v>24.7</v>
       </c>
       <c r="Q45" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R45">
         <v>256</v>
@@ -7603,7 +7579,7 @@
     </row>
     <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B46">
         <v>184</v>
@@ -7651,7 +7627,7 @@
         <v>24.9</v>
       </c>
       <c r="Q46" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R46">
         <v>255</v>
@@ -7665,7 +7641,7 @@
     </row>
     <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B47">
         <v>37</v>
@@ -7713,7 +7689,7 @@
         <v>25.4</v>
       </c>
       <c r="Q47" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R47">
         <v>254</v>
@@ -7727,7 +7703,7 @@
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B48">
         <v>99</v>
@@ -7775,7 +7751,7 @@
         <v>25.7</v>
       </c>
       <c r="Q48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R48">
         <v>253</v>
@@ -7789,7 +7765,7 @@
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B49">
         <v>44</v>
@@ -7837,7 +7813,7 @@
         <v>25.8</v>
       </c>
       <c r="Q49" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R49">
         <v>252</v>
@@ -7851,7 +7827,7 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B50">
         <v>58</v>
@@ -7899,7 +7875,7 @@
         <v>26</v>
       </c>
       <c r="Q50" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R50">
         <v>251</v>
@@ -7913,7 +7889,7 @@
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B51">
         <v>42</v>
@@ -7961,7 +7937,7 @@
         <v>26.3</v>
       </c>
       <c r="Q51" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R51">
         <v>250</v>
@@ -7975,7 +7951,7 @@
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B52">
         <v>62</v>
@@ -8023,7 +7999,7 @@
         <v>26.5</v>
       </c>
       <c r="Q52" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R52">
         <v>248</v>
@@ -8037,7 +8013,7 @@
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B53">
         <v>46</v>
@@ -8085,7 +8061,7 @@
         <v>26.5</v>
       </c>
       <c r="Q53" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R53">
         <v>249</v>
@@ -8099,7 +8075,7 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B54">
         <v>36</v>
@@ -8147,7 +8123,7 @@
         <v>26.8</v>
       </c>
       <c r="Q54" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R54">
         <v>247</v>
@@ -8161,7 +8137,7 @@
     </row>
     <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B55">
         <v>66</v>
@@ -8209,7 +8185,7 @@
         <v>27.2</v>
       </c>
       <c r="Q55" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R55">
         <v>246</v>
@@ -8223,7 +8199,7 @@
     </row>
     <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B56">
         <v>53</v>
@@ -8271,7 +8247,7 @@
         <v>27.8</v>
       </c>
       <c r="Q56" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R56">
         <v>245</v>
@@ -8285,7 +8261,7 @@
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B57">
         <v>41</v>
@@ -8333,7 +8309,7 @@
         <v>28.2</v>
       </c>
       <c r="Q57" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R57">
         <v>244</v>
@@ -8347,7 +8323,7 @@
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B58">
         <v>99</v>
@@ -8395,7 +8371,7 @@
         <v>28.4</v>
       </c>
       <c r="Q58" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R58">
         <v>243</v>
@@ -8409,7 +8385,7 @@
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B59">
         <v>56</v>
@@ -8457,7 +8433,7 @@
         <v>28.5</v>
       </c>
       <c r="Q59" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R59">
         <v>241</v>
@@ -8471,7 +8447,7 @@
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B60">
         <v>333</v>
@@ -8519,7 +8495,7 @@
         <v>28.5</v>
       </c>
       <c r="Q60" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R60">
         <v>241</v>
@@ -8533,7 +8509,7 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B61">
         <v>47</v>
@@ -8581,7 +8557,7 @@
         <v>28.6</v>
       </c>
       <c r="Q61" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R61">
         <v>240</v>
@@ -8595,7 +8571,7 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B62">
         <v>57</v>
@@ -8643,7 +8619,7 @@
         <v>29.3</v>
       </c>
       <c r="Q62" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R62">
         <v>239</v>
@@ -8657,7 +8633,7 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B63">
         <v>49</v>
@@ -8705,7 +8681,7 @@
         <v>29.6</v>
       </c>
       <c r="Q63" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R63">
         <v>238</v>
@@ -8719,7 +8695,7 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B64">
         <v>810</v>
@@ -8767,7 +8743,7 @@
         <v>29.7</v>
       </c>
       <c r="Q64" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R64">
         <v>237</v>
@@ -8781,7 +8757,7 @@
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B65">
         <v>57</v>
@@ -8829,7 +8805,7 @@
         <v>30.1</v>
       </c>
       <c r="Q65" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R65">
         <v>236</v>
@@ -8843,7 +8819,7 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B66">
         <v>478</v>
@@ -8891,7 +8867,7 @@
         <v>30.2</v>
       </c>
       <c r="Q66" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R66">
         <v>235</v>
@@ -8905,7 +8881,7 @@
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B67">
         <v>281</v>
@@ -8953,7 +8929,7 @@
         <v>30.5</v>
       </c>
       <c r="Q67" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R67">
         <v>234</v>
@@ -8967,7 +8943,7 @@
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B68">
         <v>80</v>
@@ -9015,7 +8991,7 @@
         <v>30.6</v>
       </c>
       <c r="Q68" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R68">
         <v>233</v>
@@ -9029,7 +9005,7 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B69">
         <v>170</v>
@@ -9077,7 +9053,7 @@
         <v>30.7</v>
       </c>
       <c r="Q69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R69">
         <v>231</v>
@@ -9091,7 +9067,7 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B70">
         <v>96</v>
@@ -9139,7 +9115,7 @@
         <v>30.7</v>
       </c>
       <c r="Q70" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R70">
         <v>232</v>
@@ -9153,7 +9129,7 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B71">
         <v>120</v>
@@ -9201,7 +9177,7 @@
         <v>30.8</v>
       </c>
       <c r="Q71" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R71">
         <v>230</v>
@@ -9215,7 +9191,7 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B72">
         <v>36</v>
@@ -9263,7 +9239,7 @@
         <v>31.1</v>
       </c>
       <c r="Q72" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R72">
         <v>229</v>
@@ -9277,7 +9253,7 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B73">
         <v>67</v>
@@ -9325,7 +9301,7 @@
         <v>31.5</v>
       </c>
       <c r="Q73" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R73">
         <v>228</v>
@@ -9339,7 +9315,7 @@
     </row>
     <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B74">
         <v>152</v>
@@ -9387,7 +9363,7 @@
         <v>31.7</v>
       </c>
       <c r="Q74" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R74">
         <v>227</v>
@@ -9401,7 +9377,7 @@
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B75">
         <v>46</v>
@@ -9449,7 +9425,7 @@
         <v>31.8</v>
       </c>
       <c r="Q75" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R75">
         <v>225</v>
@@ -9463,7 +9439,7 @@
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B76">
         <v>72</v>
@@ -9511,7 +9487,7 @@
         <v>31.8</v>
       </c>
       <c r="Q76" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R76">
         <v>226</v>
@@ -9525,7 +9501,7 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B77">
         <v>75</v>
@@ -9573,7 +9549,7 @@
         <v>32.6</v>
       </c>
       <c r="Q77" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R77">
         <v>224</v>
@@ -9587,7 +9563,7 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B78">
         <v>57</v>
@@ -9635,7 +9611,7 @@
         <v>32.6</v>
       </c>
       <c r="Q78" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R78">
         <v>223</v>
@@ -9649,7 +9625,7 @@
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B79">
         <v>49</v>
@@ -9697,7 +9673,7 @@
         <v>32.8</v>
       </c>
       <c r="Q79" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R79">
         <v>222</v>
@@ -9711,7 +9687,7 @@
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B80">
         <v>231</v>
@@ -9759,7 +9735,7 @@
         <v>32.9</v>
       </c>
       <c r="Q80" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R80">
         <v>221</v>
@@ -9773,7 +9749,7 @@
     </row>
     <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B81">
         <v>101</v>
@@ -9821,7 +9797,7 @@
         <v>33.7</v>
       </c>
       <c r="Q81" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R81">
         <v>220</v>
@@ -9835,7 +9811,7 @@
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B82">
         <v>114</v>
@@ -9883,7 +9859,7 @@
         <v>33.8</v>
       </c>
       <c r="Q82" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R82">
         <v>219</v>
@@ -9897,7 +9873,7 @@
     </row>
     <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B83">
         <v>38</v>
@@ -9945,7 +9921,7 @@
         <v>34.1</v>
       </c>
       <c r="Q83" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R83">
         <v>218</v>
@@ -9959,7 +9935,7 @@
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B84">
         <v>48</v>
@@ -10007,7 +9983,7 @@
         <v>34.2</v>
       </c>
       <c r="Q84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R84">
         <v>217</v>
@@ -10021,7 +9997,7 @@
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B85">
         <v>43</v>
@@ -10069,7 +10045,7 @@
         <v>34.2</v>
       </c>
       <c r="Q85" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R85">
         <v>216</v>
@@ -10083,7 +10059,7 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B86">
         <v>33</v>
@@ -10131,7 +10107,7 @@
         <v>34.6</v>
       </c>
       <c r="Q86" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R86">
         <v>215</v>
@@ -10145,7 +10121,7 @@
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B87">
         <v>395</v>
@@ -10193,7 +10169,7 @@
         <v>35.6</v>
       </c>
       <c r="Q87" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R87">
         <v>213</v>
@@ -10207,7 +10183,7 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B88">
         <v>60</v>
@@ -10255,7 +10231,7 @@
         <v>35.6</v>
       </c>
       <c r="Q88" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R88">
         <v>214</v>
@@ -10269,7 +10245,7 @@
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B89">
         <v>31</v>
@@ -10317,7 +10293,7 @@
         <v>35.8</v>
       </c>
       <c r="Q89" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R89">
         <v>212</v>
@@ -10331,7 +10307,7 @@
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B90">
         <v>43</v>
@@ -10379,7 +10355,7 @@
         <v>36.1</v>
       </c>
       <c r="Q90" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R90">
         <v>211</v>
@@ -10393,7 +10369,7 @@
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B91">
         <v>43</v>
@@ -10441,7 +10417,7 @@
         <v>36.2</v>
       </c>
       <c r="Q91" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R91">
         <v>210</v>
@@ -10455,7 +10431,7 @@
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B92">
         <v>77</v>
@@ -10503,7 +10479,7 @@
         <v>36.3</v>
       </c>
       <c r="Q92" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R92">
         <v>209</v>
@@ -10517,7 +10493,7 @@
     </row>
     <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B93">
         <v>72</v>
@@ -10565,7 +10541,7 @@
         <v>36.5</v>
       </c>
       <c r="Q93" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R93">
         <v>208</v>
@@ -10579,7 +10555,7 @@
     </row>
     <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B94">
         <v>48</v>
@@ -10627,7 +10603,7 @@
         <v>36.5</v>
       </c>
       <c r="Q94" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R94">
         <v>207</v>
@@ -10641,7 +10617,7 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B95">
         <v>34</v>
@@ -10689,7 +10665,7 @@
         <v>37.1</v>
       </c>
       <c r="Q95" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R95">
         <v>206</v>
@@ -10703,7 +10679,7 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B96">
         <v>45</v>
@@ -10751,7 +10727,7 @@
         <v>37.3</v>
       </c>
       <c r="Q96" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R96">
         <v>205</v>
@@ -10765,7 +10741,7 @@
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B97">
         <v>96</v>
@@ -10813,7 +10789,7 @@
         <v>37.9</v>
       </c>
       <c r="Q97" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R97">
         <v>204</v>
@@ -10827,7 +10803,7 @@
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B98">
         <v>106</v>
@@ -10875,7 +10851,7 @@
         <v>38.5</v>
       </c>
       <c r="Q98" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R98">
         <v>203</v>
@@ -10889,7 +10865,7 @@
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B99">
         <v>55</v>
@@ -10937,7 +10913,7 @@
         <v>38.8</v>
       </c>
       <c r="Q99" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R99">
         <v>202</v>
@@ -10951,7 +10927,7 @@
     </row>
     <row r="100" spans="1:20">
       <c r="A100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B100">
         <v>37</v>
@@ -10999,7 +10975,7 @@
         <v>39.2</v>
       </c>
       <c r="Q100" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R100">
         <v>201</v>
@@ -11013,7 +10989,7 @@
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B101">
         <v>77</v>
@@ -11061,7 +11037,7 @@
         <v>39.5</v>
       </c>
       <c r="Q101" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R101">
         <v>200</v>
@@ -11075,7 +11051,7 @@
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B102">
         <v>295</v>
@@ -11123,7 +11099,7 @@
         <v>39.7</v>
       </c>
       <c r="Q102" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R102">
         <v>199</v>
@@ -11137,7 +11113,7 @@
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B103">
         <v>44</v>
@@ -11185,7 +11161,7 @@
         <v>40.1</v>
       </c>
       <c r="Q103" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R103">
         <v>198</v>
@@ -11199,7 +11175,7 @@
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B104">
         <v>53</v>
@@ -11247,7 +11223,7 @@
         <v>40.9</v>
       </c>
       <c r="Q104" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R104">
         <v>197</v>
@@ -11261,7 +11237,7 @@
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B105">
         <v>31</v>
@@ -11309,7 +11285,7 @@
         <v>41</v>
       </c>
       <c r="Q105" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R105">
         <v>196</v>
@@ -11323,7 +11299,7 @@
     </row>
     <row r="106" spans="1:20">
       <c r="A106" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B106">
         <v>31</v>
@@ -11371,7 +11347,7 @@
         <v>41.6</v>
       </c>
       <c r="Q106" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R106">
         <v>195</v>
@@ -11385,7 +11361,7 @@
     </row>
     <row r="107" spans="1:20">
       <c r="A107" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B107">
         <v>154</v>
@@ -11433,7 +11409,7 @@
         <v>41.6</v>
       </c>
       <c r="Q107" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R107">
         <v>194</v>
@@ -11447,7 +11423,7 @@
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B108">
         <v>38</v>
@@ -11495,7 +11471,7 @@
         <v>42.2</v>
       </c>
       <c r="Q108" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R108">
         <v>193</v>
@@ -11509,7 +11485,7 @@
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B109">
         <v>53</v>
@@ -11557,7 +11533,7 @@
         <v>42.2</v>
       </c>
       <c r="Q109" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R109">
         <v>192</v>
@@ -11571,7 +11547,7 @@
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B110">
         <v>31</v>
@@ -11619,7 +11595,7 @@
         <v>42.4</v>
       </c>
       <c r="Q110" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R110">
         <v>191</v>
@@ -11633,7 +11609,7 @@
     </row>
     <row r="111" spans="1:20">
       <c r="A111" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B111">
         <v>372</v>
@@ -11681,7 +11657,7 @@
         <v>42.5</v>
       </c>
       <c r="Q111" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R111">
         <v>190</v>
@@ -11695,7 +11671,7 @@
     </row>
     <row r="112" spans="1:20">
       <c r="A112" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B112">
         <v>786</v>
@@ -11743,7 +11719,7 @@
         <v>42.9</v>
       </c>
       <c r="Q112" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R112">
         <v>189</v>
@@ -11757,7 +11733,7 @@
     </row>
     <row r="113" spans="1:20">
       <c r="A113" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B113">
         <v>51</v>
@@ -11805,7 +11781,7 @@
         <v>43.1</v>
       </c>
       <c r="Q113" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R113">
         <v>188</v>
@@ -11819,7 +11795,7 @@
     </row>
     <row r="114" spans="1:20">
       <c r="A114" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B114">
         <v>67</v>
@@ -11867,7 +11843,7 @@
         <v>43.6</v>
       </c>
       <c r="Q114" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R114">
         <v>187</v>
@@ -11881,7 +11857,7 @@
     </row>
     <row r="115" spans="1:20">
       <c r="A115" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B115">
         <v>55</v>
@@ -11929,7 +11905,7 @@
         <v>43.9</v>
       </c>
       <c r="Q115" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R115">
         <v>186</v>
@@ -11943,7 +11919,7 @@
     </row>
     <row r="116" spans="1:20">
       <c r="A116" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B116">
         <v>562</v>
@@ -11991,7 +11967,7 @@
         <v>44</v>
       </c>
       <c r="Q116" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R116">
         <v>185</v>
@@ -12005,7 +11981,7 @@
     </row>
     <row r="117" spans="1:20">
       <c r="A117" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B117">
         <v>41</v>
@@ -12053,7 +12029,7 @@
         <v>44.3</v>
       </c>
       <c r="Q117" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R117">
         <v>184</v>
@@ -12067,7 +12043,7 @@
     </row>
     <row r="118" spans="1:20">
       <c r="A118" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B118">
         <v>57</v>
@@ -12115,7 +12091,7 @@
         <v>44.5</v>
       </c>
       <c r="Q118" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R118">
         <v>183</v>
@@ -12129,7 +12105,7 @@
     </row>
     <row r="119" spans="1:20">
       <c r="A119" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B119">
         <v>67</v>
@@ -12177,7 +12153,7 @@
         <v>44.9</v>
       </c>
       <c r="Q119" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R119">
         <v>182</v>
@@ -12191,7 +12167,7 @@
     </row>
     <row r="120" spans="1:20">
       <c r="A120" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B120">
         <v>49</v>
@@ -12239,7 +12215,7 @@
         <v>45.2</v>
       </c>
       <c r="Q120" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R120">
         <v>181</v>
@@ -12253,7 +12229,7 @@
     </row>
     <row r="121" spans="1:20">
       <c r="A121" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B121">
         <v>539</v>
@@ -12301,7 +12277,7 @@
         <v>45.5</v>
       </c>
       <c r="Q121" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R121">
         <v>180</v>
@@ -12315,7 +12291,7 @@
     </row>
     <row r="122" spans="1:20">
       <c r="A122" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B122">
         <v>39</v>
@@ -12363,7 +12339,7 @@
         <v>45.6</v>
       </c>
       <c r="Q122" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R122">
         <v>178</v>
@@ -12377,7 +12353,7 @@
     </row>
     <row r="123" spans="1:20">
       <c r="A123" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B123">
         <v>38</v>
@@ -12425,7 +12401,7 @@
         <v>45.6</v>
       </c>
       <c r="Q123" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R123">
         <v>179</v>
@@ -12439,7 +12415,7 @@
     </row>
     <row r="124" spans="1:20">
       <c r="A124" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B124">
         <v>121</v>
@@ -12487,7 +12463,7 @@
         <v>45.7</v>
       </c>
       <c r="Q124" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R124">
         <v>177</v>
@@ -12501,7 +12477,7 @@
     </row>
     <row r="125" spans="1:20">
       <c r="A125" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B125">
         <v>65</v>
@@ -12549,7 +12525,7 @@
         <v>45.8</v>
       </c>
       <c r="Q125" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R125">
         <v>176</v>
@@ -12563,7 +12539,7 @@
     </row>
     <row r="126" spans="1:20">
       <c r="A126" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B126">
         <v>70</v>
@@ -12611,7 +12587,7 @@
         <v>45.9</v>
       </c>
       <c r="Q126" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R126">
         <v>173</v>
@@ -12625,7 +12601,7 @@
     </row>
     <row r="127" spans="1:20">
       <c r="A127" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B127">
         <v>166</v>
@@ -12673,7 +12649,7 @@
         <v>45.9</v>
       </c>
       <c r="Q127" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R127">
         <v>173</v>
@@ -12687,7 +12663,7 @@
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B128">
         <v>45</v>
@@ -12735,7 +12711,7 @@
         <v>45.9</v>
       </c>
       <c r="Q128" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R128">
         <v>175</v>
@@ -12749,7 +12725,7 @@
     </row>
     <row r="129" spans="1:20">
       <c r="A129" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B129">
         <v>67</v>
@@ -12797,7 +12773,7 @@
         <v>46</v>
       </c>
       <c r="Q129" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R129">
         <v>172</v>
@@ -12811,7 +12787,7 @@
     </row>
     <row r="130" spans="1:20">
       <c r="A130" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B130">
         <v>52</v>
@@ -12859,7 +12835,7 @@
         <v>46.2</v>
       </c>
       <c r="Q130" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R130">
         <v>171</v>
@@ -12873,7 +12849,7 @@
     </row>
     <row r="131" spans="1:20">
       <c r="A131" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B131">
         <v>124</v>
@@ -12921,7 +12897,7 @@
         <v>46.6</v>
       </c>
       <c r="Q131" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R131">
         <v>170</v>
@@ -12935,7 +12911,7 @@
     </row>
     <row r="132" spans="1:20">
       <c r="A132" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B132">
         <v>35</v>
@@ -12983,7 +12959,7 @@
         <v>46.8</v>
       </c>
       <c r="Q132" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R132">
         <v>169</v>
@@ -12997,7 +12973,7 @@
     </row>
     <row r="133" spans="1:20">
       <c r="A133" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B133">
         <v>261</v>
@@ -13045,7 +13021,7 @@
         <v>46.9</v>
       </c>
       <c r="Q133" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R133">
         <v>168</v>
@@ -13059,7 +13035,7 @@
     </row>
     <row r="134" spans="1:20">
       <c r="A134" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B134">
         <v>87</v>
@@ -13107,7 +13083,7 @@
         <v>47.1</v>
       </c>
       <c r="Q134" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R134">
         <v>167</v>
@@ -13121,7 +13097,7 @@
     </row>
     <row r="135" spans="1:20">
       <c r="A135" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B135">
         <v>163</v>
@@ -13169,7 +13145,7 @@
         <v>47.1</v>
       </c>
       <c r="Q135" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R135">
         <v>166</v>
@@ -13183,7 +13159,7 @@
     </row>
     <row r="136" spans="1:20">
       <c r="A136" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B136">
         <v>38</v>
@@ -13231,7 +13207,7 @@
         <v>47.4</v>
       </c>
       <c r="Q136" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R136">
         <v>165</v>
@@ -13245,7 +13221,7 @@
     </row>
     <row r="137" spans="1:20">
       <c r="A137" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B137">
         <v>179</v>
@@ -13293,7 +13269,7 @@
         <v>47.6</v>
       </c>
       <c r="Q137" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R137">
         <v>164</v>
@@ -13307,7 +13283,7 @@
     </row>
     <row r="138" spans="1:20">
       <c r="A138" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B138">
         <v>35</v>
@@ -13355,7 +13331,7 @@
         <v>48.2</v>
       </c>
       <c r="Q138" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R138">
         <v>163</v>
@@ -13369,7 +13345,7 @@
     </row>
     <row r="139" spans="1:20">
       <c r="A139" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B139">
         <v>44</v>
@@ -13417,7 +13393,7 @@
         <v>48.3</v>
       </c>
       <c r="Q139" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R139">
         <v>162</v>
@@ -13431,7 +13407,7 @@
     </row>
     <row r="140" spans="1:20">
       <c r="A140" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B140">
         <v>59</v>
@@ -13479,7 +13455,7 @@
         <v>48.6</v>
       </c>
       <c r="Q140" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R140">
         <v>161</v>
@@ -13493,7 +13469,7 @@
     </row>
     <row r="141" spans="1:20">
       <c r="A141" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B141">
         <v>62</v>
@@ -13541,7 +13517,7 @@
         <v>48.9</v>
       </c>
       <c r="Q141" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R141">
         <v>160</v>
@@ -13555,7 +13531,7 @@
     </row>
     <row r="142" spans="1:20">
       <c r="A142" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B142">
         <v>46</v>
@@ -13603,7 +13579,7 @@
         <v>49</v>
       </c>
       <c r="Q142" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R142">
         <v>159</v>
@@ -13617,7 +13593,7 @@
     </row>
     <row r="143" spans="1:20">
       <c r="A143" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B143">
         <v>65</v>
@@ -13665,7 +13641,7 @@
         <v>49.1</v>
       </c>
       <c r="Q143" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R143">
         <v>158</v>
@@ -13679,7 +13655,7 @@
     </row>
     <row r="144" spans="1:20">
       <c r="A144" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B144">
         <v>75</v>
@@ -13727,7 +13703,7 @@
         <v>49.4</v>
       </c>
       <c r="Q144" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R144">
         <v>157</v>
@@ -13741,7 +13717,7 @@
     </row>
     <row r="145" spans="1:20">
       <c r="A145" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B145">
         <v>32</v>
@@ -13789,7 +13765,7 @@
         <v>49.5</v>
       </c>
       <c r="Q145" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R145">
         <v>156</v>
@@ -13803,7 +13779,7 @@
     </row>
     <row r="146" spans="1:20">
       <c r="A146" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B146">
         <v>30</v>
@@ -13851,7 +13827,7 @@
         <v>50.5</v>
       </c>
       <c r="Q146" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R146">
         <v>155</v>
@@ -13865,7 +13841,7 @@
     </row>
     <row r="147" spans="1:20">
       <c r="A147" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B147">
         <v>36</v>
@@ -13913,7 +13889,7 @@
         <v>50.6</v>
       </c>
       <c r="Q147" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R147">
         <v>154</v>
@@ -13927,7 +13903,7 @@
     </row>
     <row r="148" spans="1:20">
       <c r="A148" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B148">
         <v>30</v>
@@ -13975,7 +13951,7 @@
         <v>50.7</v>
       </c>
       <c r="Q148" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R148">
         <v>153</v>
@@ -13989,7 +13965,7 @@
     </row>
     <row r="149" spans="1:20">
       <c r="A149" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B149">
         <v>34</v>
@@ -14037,7 +14013,7 @@
         <v>51</v>
       </c>
       <c r="Q149" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R149">
         <v>152</v>
@@ -14051,7 +14027,7 @@
     </row>
     <row r="150" spans="1:20">
       <c r="A150" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B150">
         <v>175</v>
@@ -14099,7 +14075,7 @@
         <v>51.2</v>
       </c>
       <c r="Q150" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R150">
         <v>151</v>
@@ -14113,7 +14089,7 @@
     </row>
     <row r="151" spans="1:20">
       <c r="A151" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B151">
         <v>52</v>
@@ -14161,7 +14137,7 @@
         <v>51.8</v>
       </c>
       <c r="Q151" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R151">
         <v>150</v>
@@ -14175,7 +14151,7 @@
     </row>
     <row r="152" spans="1:20">
       <c r="A152" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B152">
         <v>221</v>
@@ -14223,7 +14199,7 @@
         <v>52.4</v>
       </c>
       <c r="Q152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R152">
         <v>149</v>
@@ -14237,7 +14213,7 @@
     </row>
     <row r="153" spans="1:20">
       <c r="A153" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B153">
         <v>55</v>
@@ -14285,7 +14261,7 @@
         <v>52.7</v>
       </c>
       <c r="Q153" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R153">
         <v>146</v>
@@ -14299,7 +14275,7 @@
     </row>
     <row r="154" spans="1:20">
       <c r="A154" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B154">
         <v>40</v>
@@ -14347,7 +14323,7 @@
         <v>52.7</v>
       </c>
       <c r="Q154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R154">
         <v>147</v>
@@ -14361,7 +14337,7 @@
     </row>
     <row r="155" spans="1:20">
       <c r="A155" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B155">
         <v>45</v>
@@ -14409,7 +14385,7 @@
         <v>52.7</v>
       </c>
       <c r="Q155" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R155">
         <v>147</v>
@@ -14423,7 +14399,7 @@
     </row>
     <row r="156" spans="1:20">
       <c r="A156" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B156">
         <v>56</v>
@@ -14471,7 +14447,7 @@
         <v>52.8</v>
       </c>
       <c r="Q156" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R156">
         <v>145</v>
@@ -14485,7 +14461,7 @@
     </row>
     <row r="157" spans="1:20">
       <c r="A157" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B157">
         <v>189</v>
@@ -14533,7 +14509,7 @@
         <v>52.9</v>
       </c>
       <c r="Q157" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R157">
         <v>144</v>
@@ -14547,7 +14523,7 @@
     </row>
     <row r="158" spans="1:20">
       <c r="A158" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B158">
         <v>168</v>
@@ -14595,7 +14571,7 @@
         <v>53.2</v>
       </c>
       <c r="Q158" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R158">
         <v>143</v>
@@ -14609,7 +14585,7 @@
     </row>
     <row r="159" spans="1:20">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B159">
         <v>64</v>
@@ -14657,7 +14633,7 @@
         <v>53.3</v>
       </c>
       <c r="Q159" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R159">
         <v>142</v>
@@ -14671,7 +14647,7 @@
     </row>
     <row r="160" spans="1:20">
       <c r="A160" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B160">
         <v>51</v>
@@ -14719,7 +14695,7 @@
         <v>53.7</v>
       </c>
       <c r="Q160" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R160">
         <v>141</v>
@@ -14733,7 +14709,7 @@
     </row>
     <row r="161" spans="1:20">
       <c r="A161" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B161">
         <v>44</v>
@@ -14781,7 +14757,7 @@
         <v>53.7</v>
       </c>
       <c r="Q161" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R161">
         <v>140</v>
@@ -14795,7 +14771,7 @@
     </row>
     <row r="162" spans="1:20">
       <c r="A162" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B162">
         <v>95</v>
@@ -14843,7 +14819,7 @@
         <v>53.8</v>
       </c>
       <c r="Q162" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R162">
         <v>139</v>
@@ -14857,7 +14833,7 @@
     </row>
     <row r="163" spans="1:20">
       <c r="A163" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B163">
         <v>45</v>
@@ -14905,7 +14881,7 @@
         <v>54.9</v>
       </c>
       <c r="Q163" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R163">
         <v>138</v>
@@ -14919,7 +14895,7 @@
     </row>
     <row r="164" spans="1:20">
       <c r="A164" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B164">
         <v>56</v>
@@ -14967,7 +14943,7 @@
         <v>55.2</v>
       </c>
       <c r="Q164" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R164">
         <v>137</v>
@@ -14981,7 +14957,7 @@
     </row>
     <row r="165" spans="1:20">
       <c r="A165" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B165">
         <v>129</v>
@@ -15029,7 +15005,7 @@
         <v>55.3</v>
       </c>
       <c r="Q165" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R165">
         <v>136</v>
@@ -15043,7 +15019,7 @@
     </row>
     <row r="166" spans="1:20">
       <c r="A166" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B166">
         <v>221</v>
@@ -15091,7 +15067,7 @@
         <v>55.4</v>
       </c>
       <c r="Q166" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R166">
         <v>135</v>
@@ -15105,7 +15081,7 @@
     </row>
     <row r="167" spans="1:20">
       <c r="A167" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B167">
         <v>33</v>
@@ -15153,7 +15129,7 @@
         <v>55.5</v>
       </c>
       <c r="Q167" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R167">
         <v>134</v>
@@ -15167,7 +15143,7 @@
     </row>
     <row r="168" spans="1:20">
       <c r="A168" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B168">
         <v>34</v>
@@ -15215,7 +15191,7 @@
         <v>56.1</v>
       </c>
       <c r="Q168" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R168">
         <v>133</v>
@@ -15229,7 +15205,7 @@
     </row>
     <row r="169" spans="1:20">
       <c r="A169" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B169">
         <v>35</v>
@@ -15277,7 +15253,7 @@
         <v>56.4</v>
       </c>
       <c r="Q169" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R169">
         <v>132</v>
@@ -15291,7 +15267,7 @@
     </row>
     <row r="170" spans="1:20">
       <c r="A170" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B170">
         <v>44</v>
@@ -15339,7 +15315,7 @@
         <v>56.5</v>
       </c>
       <c r="Q170" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R170">
         <v>131</v>
@@ -15353,7 +15329,7 @@
     </row>
     <row r="171" spans="1:20">
       <c r="A171" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B171">
         <v>36</v>
@@ -15401,7 +15377,7 @@
         <v>56.5</v>
       </c>
       <c r="Q171" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R171">
         <v>130</v>
@@ -15415,7 +15391,7 @@
     </row>
     <row r="172" spans="1:20">
       <c r="A172" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B172">
         <v>34</v>
@@ -15463,7 +15439,7 @@
         <v>56.7</v>
       </c>
       <c r="Q172" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R172">
         <v>129</v>
@@ -15477,7 +15453,7 @@
     </row>
     <row r="173" spans="1:20">
       <c r="A173" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B173">
         <v>92</v>
@@ -15525,7 +15501,7 @@
         <v>57.1</v>
       </c>
       <c r="Q173" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R173">
         <v>128</v>
@@ -15539,7 +15515,7 @@
     </row>
     <row r="174" spans="1:20">
       <c r="A174" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B174">
         <v>35</v>
@@ -15587,7 +15563,7 @@
         <v>57.2</v>
       </c>
       <c r="Q174" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R174">
         <v>127</v>
@@ -15601,7 +15577,7 @@
     </row>
     <row r="175" spans="1:20">
       <c r="A175" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B175">
         <v>116</v>
@@ -15649,7 +15625,7 @@
         <v>57.4</v>
       </c>
       <c r="Q175" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R175">
         <v>126</v>
@@ -15663,7 +15639,7 @@
     </row>
     <row r="176" spans="1:20">
       <c r="A176" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B176">
         <v>35</v>
@@ -15711,7 +15687,7 @@
         <v>57.4</v>
       </c>
       <c r="Q176" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R176">
         <v>125</v>
@@ -15725,7 +15701,7 @@
     </row>
     <row r="177" spans="1:20">
       <c r="A177" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B177">
         <v>64</v>
@@ -15773,7 +15749,7 @@
         <v>57.6</v>
       </c>
       <c r="Q177" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R177">
         <v>124</v>
@@ -15787,7 +15763,7 @@
     </row>
     <row r="178" spans="1:20">
       <c r="A178" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B178">
         <v>111</v>
@@ -15835,7 +15811,7 @@
         <v>57.8</v>
       </c>
       <c r="Q178" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R178">
         <v>123</v>
@@ -15849,7 +15825,7 @@
     </row>
     <row r="179" spans="1:20">
       <c r="A179" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B179">
         <v>73</v>
@@ -15897,7 +15873,7 @@
         <v>58.1</v>
       </c>
       <c r="Q179" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R179">
         <v>121</v>
@@ -15911,7 +15887,7 @@
     </row>
     <row r="180" spans="1:20">
       <c r="A180" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B180">
         <v>45</v>
@@ -15959,7 +15935,7 @@
         <v>58.1</v>
       </c>
       <c r="Q180" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R180">
         <v>122</v>
@@ -15973,7 +15949,7 @@
     </row>
     <row r="181" spans="1:20">
       <c r="A181" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B181">
         <v>31</v>
@@ -16021,7 +15997,7 @@
         <v>58.2</v>
       </c>
       <c r="Q181" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R181">
         <v>120</v>
@@ -16035,7 +16011,7 @@
     </row>
     <row r="182" spans="1:20">
       <c r="A182" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B182">
         <v>36</v>
@@ -16083,7 +16059,7 @@
         <v>58.3</v>
       </c>
       <c r="Q182" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R182">
         <v>119</v>
@@ -16097,7 +16073,7 @@
     </row>
     <row r="183" spans="1:20">
       <c r="A183" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B183">
         <v>46</v>
@@ -16145,7 +16121,7 @@
         <v>58.4</v>
       </c>
       <c r="Q183" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R183">
         <v>118</v>
@@ -16159,7 +16135,7 @@
     </row>
     <row r="184" spans="1:20">
       <c r="A184" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B184">
         <v>43</v>
@@ -16207,7 +16183,7 @@
         <v>58.5</v>
       </c>
       <c r="Q184" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R184">
         <v>117</v>
@@ -16221,7 +16197,7 @@
     </row>
     <row r="185" spans="1:20">
       <c r="A185" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B185">
         <v>31</v>
@@ -16269,7 +16245,7 @@
         <v>59</v>
       </c>
       <c r="Q185" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R185">
         <v>116</v>
@@ -16283,7 +16259,7 @@
     </row>
     <row r="186" spans="1:20">
       <c r="A186" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B186">
         <v>34</v>
@@ -16331,7 +16307,7 @@
         <v>59.3</v>
       </c>
       <c r="Q186" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R186">
         <v>115</v>
@@ -16345,7 +16321,7 @@
     </row>
     <row r="187" spans="1:20">
       <c r="A187" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B187">
         <v>32</v>
@@ -16393,7 +16369,7 @@
         <v>59.4</v>
       </c>
       <c r="Q187" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R187">
         <v>114</v>
@@ -16407,7 +16383,7 @@
     </row>
     <row r="188" spans="1:20">
       <c r="A188" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B188">
         <v>38</v>
@@ -16455,7 +16431,7 @@
         <v>59.8</v>
       </c>
       <c r="Q188" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R188">
         <v>113</v>
@@ -16469,7 +16445,7 @@
     </row>
     <row r="189" spans="1:20">
       <c r="A189" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B189">
         <v>517</v>
@@ -16517,7 +16493,7 @@
         <v>60.1</v>
       </c>
       <c r="Q189" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R189">
         <v>111</v>
@@ -16531,7 +16507,7 @@
     </row>
     <row r="190" spans="1:20">
       <c r="A190" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B190">
         <v>114</v>
@@ -16579,7 +16555,7 @@
         <v>60.1</v>
       </c>
       <c r="Q190" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R190">
         <v>112</v>
@@ -16593,7 +16569,7 @@
     </row>
     <row r="191" spans="1:20">
       <c r="A191" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B191">
         <v>57</v>
@@ -16641,7 +16617,7 @@
         <v>60.3</v>
       </c>
       <c r="Q191" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R191">
         <v>110</v>
@@ -16655,7 +16631,7 @@
     </row>
     <row r="192" spans="1:20">
       <c r="A192" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B192">
         <v>226</v>
@@ -16703,7 +16679,7 @@
         <v>60.7</v>
       </c>
       <c r="Q192" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R192">
         <v>109</v>
@@ -16717,7 +16693,7 @@
     </row>
     <row r="193" spans="1:20">
       <c r="A193" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B193">
         <v>107</v>
@@ -16765,7 +16741,7 @@
         <v>61.4</v>
       </c>
       <c r="Q193" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R193">
         <v>108</v>
@@ -16779,7 +16755,7 @@
     </row>
     <row r="194" spans="1:20">
       <c r="A194" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B194">
         <v>74</v>
@@ -16827,7 +16803,7 @@
         <v>61.5</v>
       </c>
       <c r="Q194" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R194">
         <v>106</v>
@@ -16841,7 +16817,7 @@
     </row>
     <row r="195" spans="1:20">
       <c r="A195" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B195">
         <v>91</v>
@@ -16889,7 +16865,7 @@
         <v>61.5</v>
       </c>
       <c r="Q195" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R195">
         <v>107</v>
@@ -16903,7 +16879,7 @@
     </row>
     <row r="196" spans="1:20">
       <c r="A196" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B196">
         <v>32</v>
@@ -16951,7 +16927,7 @@
         <v>61.6</v>
       </c>
       <c r="Q196" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R196">
         <v>104</v>
@@ -16965,7 +16941,7 @@
     </row>
     <row r="197" spans="1:20">
       <c r="A197" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B197">
         <v>41</v>
@@ -17013,7 +16989,7 @@
         <v>61.6</v>
       </c>
       <c r="Q197" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R197">
         <v>105</v>
@@ -17027,7 +17003,7 @@
     </row>
     <row r="198" spans="1:20">
       <c r="A198" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B198">
         <v>43</v>
@@ -17075,7 +17051,7 @@
         <v>61.7</v>
       </c>
       <c r="Q198" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R198">
         <v>103</v>
@@ -17089,7 +17065,7 @@
     </row>
     <row r="199" spans="1:20">
       <c r="A199" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B199">
         <v>37</v>
@@ -17137,7 +17113,7 @@
         <v>61.8</v>
       </c>
       <c r="Q199" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R199">
         <v>102</v>
@@ -17151,7 +17127,7 @@
     </row>
     <row r="200" spans="1:20">
       <c r="A200" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B200">
         <v>31</v>
@@ -17199,7 +17175,7 @@
         <v>61.9</v>
       </c>
       <c r="Q200" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R200">
         <v>101</v>
@@ -17213,7 +17189,7 @@
     </row>
     <row r="201" spans="1:20">
       <c r="A201" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B201">
         <v>65</v>
@@ -17261,7 +17237,7 @@
         <v>62.2</v>
       </c>
       <c r="Q201" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R201">
         <v>100</v>
@@ -17275,7 +17251,7 @@
     </row>
     <row r="202" spans="1:20">
       <c r="A202" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B202">
         <v>61</v>
@@ -17323,7 +17299,7 @@
         <v>62.8</v>
       </c>
       <c r="Q202" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R202">
         <v>99</v>
@@ -17337,7 +17313,7 @@
     </row>
     <row r="203" spans="1:20">
       <c r="A203" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B203">
         <v>36</v>
@@ -17385,7 +17361,7 @@
         <v>62.9</v>
       </c>
       <c r="Q203" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R203">
         <v>98</v>
@@ -17399,7 +17375,7 @@
     </row>
     <row r="204" spans="1:20">
       <c r="A204" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B204">
         <v>38</v>
@@ -17447,7 +17423,7 @@
         <v>63</v>
       </c>
       <c r="Q204" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R204">
         <v>97</v>
@@ -17461,7 +17437,7 @@
     </row>
     <row r="205" spans="1:20">
       <c r="A205" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B205">
         <v>87</v>
@@ -17509,7 +17485,7 @@
         <v>63.2</v>
       </c>
       <c r="Q205" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R205">
         <v>96</v>
@@ -17523,7 +17499,7 @@
     </row>
     <row r="206" spans="1:20">
       <c r="A206" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B206">
         <v>104</v>
@@ -17571,7 +17547,7 @@
         <v>63.9</v>
       </c>
       <c r="Q206" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R206">
         <v>94</v>
@@ -17585,7 +17561,7 @@
     </row>
     <row r="207" spans="1:20">
       <c r="A207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B207">
         <v>30</v>
@@ -17633,7 +17609,7 @@
         <v>63.9</v>
       </c>
       <c r="Q207" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R207">
         <v>95</v>
@@ -17647,7 +17623,7 @@
     </row>
     <row r="208" spans="1:20">
       <c r="A208" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B208">
         <v>51</v>
@@ -17695,7 +17671,7 @@
         <v>64.7</v>
       </c>
       <c r="Q208" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R208">
         <v>93</v>
@@ -17709,7 +17685,7 @@
     </row>
     <row r="209" spans="1:20">
       <c r="A209" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B209">
         <v>85</v>
@@ -17757,7 +17733,7 @@
         <v>65</v>
       </c>
       <c r="Q209" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R209">
         <v>92</v>
@@ -17771,7 +17747,7 @@
     </row>
     <row r="210" spans="1:20">
       <c r="A210" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B210">
         <v>37</v>
@@ -17819,7 +17795,7 @@
         <v>65.09999999999999</v>
       </c>
       <c r="Q210" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R210">
         <v>91</v>
@@ -17833,7 +17809,7 @@
     </row>
     <row r="211" spans="1:20">
       <c r="A211" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B211">
         <v>92</v>
@@ -17881,7 +17857,7 @@
         <v>65.2</v>
       </c>
       <c r="Q211" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R211">
         <v>90</v>
@@ -17895,7 +17871,7 @@
     </row>
     <row r="212" spans="1:20">
       <c r="A212" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B212">
         <v>64</v>
@@ -17943,7 +17919,7 @@
         <v>65.59999999999999</v>
       </c>
       <c r="Q212" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R212">
         <v>89</v>
@@ -17957,7 +17933,7 @@
     </row>
     <row r="213" spans="1:20">
       <c r="A213" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B213">
         <v>36</v>
@@ -18005,7 +17981,7 @@
         <v>66</v>
       </c>
       <c r="Q213" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R213">
         <v>87</v>
@@ -18019,7 +17995,7 @@
     </row>
     <row r="214" spans="1:20">
       <c r="A214" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B214">
         <v>303</v>
@@ -18067,7 +18043,7 @@
         <v>66</v>
       </c>
       <c r="Q214" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R214">
         <v>86</v>
@@ -18081,7 +18057,7 @@
     </row>
     <row r="215" spans="1:20">
       <c r="A215" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B215">
         <v>41</v>
@@ -18129,7 +18105,7 @@
         <v>66</v>
       </c>
       <c r="Q215" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R215">
         <v>87</v>
@@ -18143,7 +18119,7 @@
     </row>
     <row r="216" spans="1:20">
       <c r="A216" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B216">
         <v>87</v>
@@ -18191,7 +18167,7 @@
         <v>66.2</v>
       </c>
       <c r="Q216" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R216">
         <v>85</v>
@@ -18205,7 +18181,7 @@
     </row>
     <row r="217" spans="1:20">
       <c r="A217" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B217">
         <v>76</v>
@@ -18253,7 +18229,7 @@
         <v>66.5</v>
       </c>
       <c r="Q217" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R217">
         <v>84</v>
@@ -18267,7 +18243,7 @@
     </row>
     <row r="218" spans="1:20">
       <c r="A218" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B218">
         <v>30</v>
@@ -18315,7 +18291,7 @@
         <v>66.7</v>
       </c>
       <c r="Q218" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R218">
         <v>83</v>
@@ -18329,7 +18305,7 @@
     </row>
     <row r="219" spans="1:20">
       <c r="A219" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B219">
         <v>50</v>
@@ -18377,7 +18353,7 @@
         <v>66.8</v>
       </c>
       <c r="Q219" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R219">
         <v>82</v>
@@ -18391,7 +18367,7 @@
     </row>
     <row r="220" spans="1:20">
       <c r="A220" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B220">
         <v>107</v>
@@ -18439,7 +18415,7 @@
         <v>67</v>
       </c>
       <c r="Q220" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R220">
         <v>81</v>
@@ -18453,7 +18429,7 @@
     </row>
     <row r="221" spans="1:20">
       <c r="A221" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B221">
         <v>35</v>
@@ -18501,7 +18477,7 @@
         <v>67</v>
       </c>
       <c r="Q221" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R221">
         <v>80</v>
@@ -18515,7 +18491,7 @@
     </row>
     <row r="222" spans="1:20">
       <c r="A222" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B222">
         <v>34</v>
@@ -18563,7 +18539,7 @@
         <v>67.09999999999999</v>
       </c>
       <c r="Q222" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R222">
         <v>79</v>
@@ -18577,7 +18553,7 @@
     </row>
     <row r="223" spans="1:20">
       <c r="A223" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B223">
         <v>130</v>
@@ -18625,7 +18601,7 @@
         <v>67.09999999999999</v>
       </c>
       <c r="Q223" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R223">
         <v>78</v>
@@ -18639,7 +18615,7 @@
     </row>
     <row r="224" spans="1:20">
       <c r="A224" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B224">
         <v>42</v>
@@ -18687,7 +18663,7 @@
         <v>67.3</v>
       </c>
       <c r="Q224" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R224">
         <v>77</v>
@@ -18701,7 +18677,7 @@
     </row>
     <row r="225" spans="1:20">
       <c r="A225" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B225">
         <v>85</v>
@@ -18749,7 +18725,7 @@
         <v>67.5</v>
       </c>
       <c r="Q225" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R225">
         <v>76</v>
@@ -18763,7 +18739,7 @@
     </row>
     <row r="226" spans="1:20">
       <c r="A226" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B226">
         <v>31</v>
@@ -18811,7 +18787,7 @@
         <v>68</v>
       </c>
       <c r="Q226" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R226">
         <v>75</v>
@@ -18825,7 +18801,7 @@
     </row>
     <row r="227" spans="1:20">
       <c r="A227" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B227">
         <v>33</v>
@@ -18873,7 +18849,7 @@
         <v>68.09999999999999</v>
       </c>
       <c r="Q227" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R227">
         <v>74</v>
@@ -18887,7 +18863,7 @@
     </row>
     <row r="228" spans="1:20">
       <c r="A228" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B228">
         <v>31</v>
@@ -18935,7 +18911,7 @@
         <v>68.2</v>
       </c>
       <c r="Q228" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R228">
         <v>72</v>
@@ -18949,7 +18925,7 @@
     </row>
     <row r="229" spans="1:20">
       <c r="A229" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B229">
         <v>80</v>
@@ -18997,7 +18973,7 @@
         <v>68.2</v>
       </c>
       <c r="Q229" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R229">
         <v>73</v>
@@ -19011,7 +18987,7 @@
     </row>
     <row r="230" spans="1:20">
       <c r="A230" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B230">
         <v>151</v>
@@ -19059,7 +19035,7 @@
         <v>68.59999999999999</v>
       </c>
       <c r="Q230" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R230">
         <v>71</v>
@@ -19073,7 +19049,7 @@
     </row>
     <row r="231" spans="1:20">
       <c r="A231" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B231">
         <v>46</v>
@@ -19121,7 +19097,7 @@
         <v>68.7</v>
       </c>
       <c r="Q231" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R231">
         <v>70</v>
@@ -19135,7 +19111,7 @@
     </row>
     <row r="232" spans="1:20">
       <c r="A232" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B232">
         <v>33</v>
@@ -19183,7 +19159,7 @@
         <v>68.8</v>
       </c>
       <c r="Q232" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R232">
         <v>69</v>
@@ -19197,7 +19173,7 @@
     </row>
     <row r="233" spans="1:20">
       <c r="A233" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B233">
         <v>225</v>
@@ -19245,7 +19221,7 @@
         <v>69</v>
       </c>
       <c r="Q233" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R233">
         <v>68</v>
@@ -19259,7 +19235,7 @@
     </row>
     <row r="234" spans="1:20">
       <c r="A234" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B234">
         <v>74</v>
@@ -19307,7 +19283,7 @@
         <v>69.2</v>
       </c>
       <c r="Q234" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R234">
         <v>67</v>
@@ -19321,7 +19297,7 @@
     </row>
     <row r="235" spans="1:20">
       <c r="A235" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B235">
         <v>39</v>
@@ -19369,7 +19345,7 @@
         <v>69.7</v>
       </c>
       <c r="Q235" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R235">
         <v>65</v>
@@ -19383,7 +19359,7 @@
     </row>
     <row r="236" spans="1:20">
       <c r="A236" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B236">
         <v>34</v>
@@ -19431,7 +19407,7 @@
         <v>69.7</v>
       </c>
       <c r="Q236" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R236">
         <v>66</v>
@@ -19445,7 +19421,7 @@
     </row>
     <row r="237" spans="1:20">
       <c r="A237" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B237">
         <v>51</v>
@@ -19493,7 +19469,7 @@
         <v>69.8</v>
       </c>
       <c r="Q237" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R237">
         <v>63</v>
@@ -19507,7 +19483,7 @@
     </row>
     <row r="238" spans="1:20">
       <c r="A238" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B238">
         <v>451</v>
@@ -19555,7 +19531,7 @@
         <v>69.8</v>
       </c>
       <c r="Q238" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R238">
         <v>63</v>
@@ -19569,7 +19545,7 @@
     </row>
     <row r="239" spans="1:20">
       <c r="A239" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B239">
         <v>43</v>
@@ -19617,7 +19593,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="Q239" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R239">
         <v>62</v>
@@ -19631,7 +19607,7 @@
     </row>
     <row r="240" spans="1:20">
       <c r="A240" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B240">
         <v>36</v>
@@ -19679,7 +19655,7 @@
         <v>71.09999999999999</v>
       </c>
       <c r="Q240" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R240">
         <v>61</v>
@@ -19693,7 +19669,7 @@
     </row>
     <row r="241" spans="1:20">
       <c r="A241" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B241">
         <v>41</v>
@@ -19741,7 +19717,7 @@
         <v>71.3</v>
       </c>
       <c r="Q241" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R241">
         <v>60</v>
@@ -19755,7 +19731,7 @@
     </row>
     <row r="242" spans="1:20">
       <c r="A242" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B242">
         <v>95</v>
@@ -19803,7 +19779,7 @@
         <v>71.7</v>
       </c>
       <c r="Q242" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R242">
         <v>59</v>
@@ -19817,7 +19793,7 @@
     </row>
     <row r="243" spans="1:20">
       <c r="A243" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B243">
         <v>78</v>
@@ -19865,7 +19841,7 @@
         <v>71.8</v>
       </c>
       <c r="Q243" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R243">
         <v>58</v>
@@ -19879,7 +19855,7 @@
     </row>
     <row r="244" spans="1:20">
       <c r="A244" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B244">
         <v>73</v>
@@ -19927,7 +19903,7 @@
         <v>71.90000000000001</v>
       </c>
       <c r="Q244" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R244">
         <v>57</v>
@@ -19941,7 +19917,7 @@
     </row>
     <row r="245" spans="1:20">
       <c r="A245" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B245">
         <v>293</v>
@@ -19989,7 +19965,7 @@
         <v>72.5</v>
       </c>
       <c r="Q245" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R245">
         <v>56</v>
@@ -20003,7 +19979,7 @@
     </row>
     <row r="246" spans="1:20">
       <c r="A246" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B246">
         <v>43</v>
@@ -20051,7 +20027,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="Q246" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R246">
         <v>55</v>
@@ -20065,7 +20041,7 @@
     </row>
     <row r="247" spans="1:20">
       <c r="A247" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B247">
         <v>44</v>
@@ -20113,7 +20089,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="Q247" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R247">
         <v>54</v>
@@ -20127,7 +20103,7 @@
     </row>
     <row r="248" spans="1:20">
       <c r="A248" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B248">
         <v>74</v>
@@ -20175,7 +20151,7 @@
         <v>73.3</v>
       </c>
       <c r="Q248" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R248">
         <v>53</v>
@@ -20189,7 +20165,7 @@
     </row>
     <row r="249" spans="1:20">
       <c r="A249" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B249">
         <v>32</v>
@@ -20237,7 +20213,7 @@
         <v>74</v>
       </c>
       <c r="Q249" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R249">
         <v>51</v>
@@ -20251,7 +20227,7 @@
     </row>
     <row r="250" spans="1:20">
       <c r="A250" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B250">
         <v>135</v>
@@ -20299,7 +20275,7 @@
         <v>74</v>
       </c>
       <c r="Q250" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R250">
         <v>52</v>
@@ -20313,7 +20289,7 @@
     </row>
     <row r="251" spans="1:20">
       <c r="A251" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B251">
         <v>155</v>
@@ -20361,7 +20337,7 @@
         <v>74.2</v>
       </c>
       <c r="Q251" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R251">
         <v>50</v>
@@ -20375,7 +20351,7 @@
     </row>
     <row r="252" spans="1:20">
       <c r="A252" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B252">
         <v>238</v>
@@ -20423,7 +20399,7 @@
         <v>74.40000000000001</v>
       </c>
       <c r="Q252" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R252">
         <v>49</v>
@@ -20437,7 +20413,7 @@
     </row>
     <row r="253" spans="1:20">
       <c r="A253" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B253">
         <v>37</v>
@@ -20485,7 +20461,7 @@
         <v>74.5</v>
       </c>
       <c r="Q253" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R253">
         <v>48</v>
@@ -20499,7 +20475,7 @@
     </row>
     <row r="254" spans="1:20">
       <c r="A254" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B254">
         <v>67</v>
@@ -20547,7 +20523,7 @@
         <v>74.59999999999999</v>
       </c>
       <c r="Q254" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R254">
         <v>47</v>
@@ -20561,7 +20537,7 @@
     </row>
     <row r="255" spans="1:20">
       <c r="A255" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B255">
         <v>53</v>
@@ -20609,7 +20585,7 @@
         <v>74.8</v>
       </c>
       <c r="Q255" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R255">
         <v>46</v>
@@ -20623,7 +20599,7 @@
     </row>
     <row r="256" spans="1:20">
       <c r="A256" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B256">
         <v>45</v>
@@ -20671,7 +20647,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="Q256" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R256">
         <v>45</v>
@@ -20685,7 +20661,7 @@
     </row>
     <row r="257" spans="1:20">
       <c r="A257" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B257">
         <v>53</v>
@@ -20733,7 +20709,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="Q257" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R257">
         <v>44</v>
@@ -20747,7 +20723,7 @@
     </row>
     <row r="258" spans="1:20">
       <c r="A258" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B258">
         <v>36</v>
@@ -20795,7 +20771,7 @@
         <v>75.3</v>
       </c>
       <c r="Q258" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R258">
         <v>43</v>
@@ -20809,7 +20785,7 @@
     </row>
     <row r="259" spans="1:20">
       <c r="A259" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B259">
         <v>33</v>
@@ -20857,7 +20833,7 @@
         <v>75.3</v>
       </c>
       <c r="Q259" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R259">
         <v>42</v>
@@ -20871,7 +20847,7 @@
     </row>
     <row r="260" spans="1:20">
       <c r="A260" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B260">
         <v>93</v>
@@ -20919,7 +20895,7 @@
         <v>76</v>
       </c>
       <c r="Q260" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R260">
         <v>41</v>
@@ -20933,7 +20909,7 @@
     </row>
     <row r="261" spans="1:20">
       <c r="A261" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B261">
         <v>79</v>
@@ -20981,7 +20957,7 @@
         <v>76.09999999999999</v>
       </c>
       <c r="Q261" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R261">
         <v>40</v>
@@ -20995,7 +20971,7 @@
     </row>
     <row r="262" spans="1:20">
       <c r="A262" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B262">
         <v>49</v>
@@ -21043,7 +21019,7 @@
         <v>76.3</v>
       </c>
       <c r="Q262" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R262">
         <v>39</v>
@@ -21057,7 +21033,7 @@
     </row>
     <row r="263" spans="1:20">
       <c r="A263" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B263">
         <v>31</v>
@@ -21105,7 +21081,7 @@
         <v>77.2</v>
       </c>
       <c r="Q263" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R263">
         <v>38</v>
@@ -21119,7 +21095,7 @@
     </row>
     <row r="264" spans="1:20">
       <c r="A264" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B264">
         <v>61</v>
@@ -21167,7 +21143,7 @@
         <v>77.2</v>
       </c>
       <c r="Q264" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R264">
         <v>37</v>
@@ -21181,7 +21157,7 @@
     </row>
     <row r="265" spans="1:20">
       <c r="A265" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B265">
         <v>39</v>
@@ -21229,7 +21205,7 @@
         <v>77.7</v>
       </c>
       <c r="Q265" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R265">
         <v>36</v>
@@ -21243,7 +21219,7 @@
     </row>
     <row r="266" spans="1:20">
       <c r="A266" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B266">
         <v>46</v>
@@ -21291,7 +21267,7 @@
         <v>78</v>
       </c>
       <c r="Q266" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R266">
         <v>35</v>
@@ -21305,7 +21281,7 @@
     </row>
     <row r="267" spans="1:20">
       <c r="A267" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B267">
         <v>90</v>
@@ -21353,7 +21329,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="Q267" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R267">
         <v>34</v>
@@ -21367,7 +21343,7 @@
     </row>
     <row r="268" spans="1:20">
       <c r="A268" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B268">
         <v>106</v>
@@ -21415,7 +21391,7 @@
         <v>78.3</v>
       </c>
       <c r="Q268" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R268">
         <v>33</v>
@@ -21429,7 +21405,7 @@
     </row>
     <row r="269" spans="1:20">
       <c r="A269" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B269">
         <v>114</v>
@@ -21477,7 +21453,7 @@
         <v>78.59999999999999</v>
       </c>
       <c r="Q269" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R269">
         <v>32</v>
@@ -21491,7 +21467,7 @@
     </row>
     <row r="270" spans="1:20">
       <c r="A270" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B270">
         <v>44</v>
@@ -21539,7 +21515,7 @@
         <v>79.5</v>
       </c>
       <c r="Q270" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R270">
         <v>31</v>
@@ -21553,7 +21529,7 @@
     </row>
     <row r="271" spans="1:20">
       <c r="A271" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B271">
         <v>41</v>
@@ -21601,7 +21577,7 @@
         <v>79.7</v>
       </c>
       <c r="Q271" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R271">
         <v>29</v>
@@ -21615,7 +21591,7 @@
     </row>
     <row r="272" spans="1:20">
       <c r="A272" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B272">
         <v>34</v>
@@ -21663,7 +21639,7 @@
         <v>79.7</v>
       </c>
       <c r="Q272" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R272">
         <v>29</v>
@@ -21677,7 +21653,7 @@
     </row>
     <row r="273" spans="1:20">
       <c r="A273" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B273">
         <v>88</v>
@@ -21725,7 +21701,7 @@
         <v>79.8</v>
       </c>
       <c r="Q273" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R273">
         <v>28</v>
@@ -21739,7 +21715,7 @@
     </row>
     <row r="274" spans="1:20">
       <c r="A274" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B274">
         <v>35</v>
@@ -21787,7 +21763,7 @@
         <v>79.90000000000001</v>
       </c>
       <c r="Q274" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R274">
         <v>26</v>
@@ -21801,7 +21777,7 @@
     </row>
     <row r="275" spans="1:20">
       <c r="A275" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B275">
         <v>32</v>
@@ -21849,7 +21825,7 @@
         <v>79.90000000000001</v>
       </c>
       <c r="Q275" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R275">
         <v>27</v>
@@ -21863,7 +21839,7 @@
     </row>
     <row r="276" spans="1:20">
       <c r="A276" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B276">
         <v>129</v>
@@ -21911,7 +21887,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="Q276" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R276">
         <v>25</v>
@@ -21925,7 +21901,7 @@
     </row>
     <row r="277" spans="1:20">
       <c r="A277" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B277">
         <v>61</v>
@@ -21973,7 +21949,7 @@
         <v>81.3</v>
       </c>
       <c r="Q277" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R277">
         <v>24</v>
@@ -21987,7 +21963,7 @@
     </row>
     <row r="278" spans="1:20">
       <c r="A278" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B278">
         <v>38</v>
@@ -22035,7 +22011,7 @@
         <v>81.5</v>
       </c>
       <c r="Q278" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R278">
         <v>23</v>
@@ -22049,7 +22025,7 @@
     </row>
     <row r="279" spans="1:20">
       <c r="A279" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B279">
         <v>34</v>
@@ -22097,7 +22073,7 @@
         <v>82.5</v>
       </c>
       <c r="Q279" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R279">
         <v>21</v>
@@ -22111,7 +22087,7 @@
     </row>
     <row r="280" spans="1:20">
       <c r="A280" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B280">
         <v>166</v>
@@ -22159,7 +22135,7 @@
         <v>82.5</v>
       </c>
       <c r="Q280" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R280">
         <v>22</v>
@@ -22173,7 +22149,7 @@
     </row>
     <row r="281" spans="1:20">
       <c r="A281" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B281">
         <v>45</v>
@@ -22221,7 +22197,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="Q281" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R281">
         <v>20</v>
@@ -22235,7 +22211,7 @@
     </row>
     <row r="282" spans="1:20">
       <c r="A282" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B282">
         <v>32</v>
@@ -22283,7 +22259,7 @@
         <v>83.7</v>
       </c>
       <c r="Q282" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R282">
         <v>19</v>
@@ -22297,7 +22273,7 @@
     </row>
     <row r="283" spans="1:20">
       <c r="A283" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B283">
         <v>54</v>
@@ -22345,7 +22321,7 @@
         <v>83.8</v>
       </c>
       <c r="Q283" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R283">
         <v>18</v>
@@ -22359,7 +22335,7 @@
     </row>
     <row r="284" spans="1:20">
       <c r="A284" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B284">
         <v>32</v>
@@ -22407,7 +22383,7 @@
         <v>83.90000000000001</v>
       </c>
       <c r="Q284" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R284">
         <v>17</v>
@@ -22421,7 +22397,7 @@
     </row>
     <row r="285" spans="1:20">
       <c r="A285" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B285">
         <v>37</v>
@@ -22469,7 +22445,7 @@
         <v>84.2</v>
       </c>
       <c r="Q285" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R285">
         <v>16</v>
@@ -22483,7 +22459,7 @@
     </row>
     <row r="286" spans="1:20">
       <c r="A286" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B286">
         <v>39</v>
@@ -22531,7 +22507,7 @@
         <v>84.3</v>
       </c>
       <c r="Q286" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R286">
         <v>15</v>
@@ -22545,7 +22521,7 @@
     </row>
     <row r="287" spans="1:20">
       <c r="A287" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B287">
         <v>37</v>
@@ -22593,7 +22569,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="Q287" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R287">
         <v>14</v>
@@ -22607,7 +22583,7 @@
     </row>
     <row r="288" spans="1:20">
       <c r="A288" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B288">
         <v>55</v>
@@ -22655,7 +22631,7 @@
         <v>85.2</v>
       </c>
       <c r="Q288" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R288">
         <v>13</v>
@@ -22669,7 +22645,7 @@
     </row>
     <row r="289" spans="1:20">
       <c r="A289" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B289">
         <v>283</v>
@@ -22717,7 +22693,7 @@
         <v>85.5</v>
       </c>
       <c r="Q289" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R289">
         <v>12</v>
@@ -22731,7 +22707,7 @@
     </row>
     <row r="290" spans="1:20">
       <c r="A290" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B290">
         <v>31</v>
@@ -22779,7 +22755,7 @@
         <v>85.7</v>
       </c>
       <c r="Q290" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R290">
         <v>11</v>
@@ -22793,7 +22769,7 @@
     </row>
     <row r="291" spans="1:20">
       <c r="A291" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B291">
         <v>83</v>
@@ -22841,7 +22817,7 @@
         <v>86</v>
       </c>
       <c r="Q291" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R291">
         <v>10</v>
@@ -22855,7 +22831,7 @@
     </row>
     <row r="292" spans="1:20">
       <c r="A292" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B292">
         <v>54</v>
@@ -22903,7 +22879,7 @@
         <v>86.2</v>
       </c>
       <c r="Q292" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R292">
         <v>9</v>
@@ -22917,7 +22893,7 @@
     </row>
     <row r="293" spans="1:20">
       <c r="A293" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B293">
         <v>77</v>
@@ -22965,7 +22941,7 @@
         <v>86.7</v>
       </c>
       <c r="Q293" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R293">
         <v>8</v>
@@ -22979,7 +22955,7 @@
     </row>
     <row r="294" spans="1:20">
       <c r="A294" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B294">
         <v>65</v>
@@ -23027,7 +23003,7 @@
         <v>87.2</v>
       </c>
       <c r="Q294" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R294">
         <v>7</v>
@@ -23041,7 +23017,7 @@
     </row>
     <row r="295" spans="1:20">
       <c r="A295" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B295">
         <v>30</v>
@@ -23089,7 +23065,7 @@
         <v>88.90000000000001</v>
       </c>
       <c r="Q295" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R295">
         <v>6</v>
@@ -23103,7 +23079,7 @@
     </row>
     <row r="296" spans="1:20">
       <c r="A296" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B296">
         <v>84</v>
@@ -23151,7 +23127,7 @@
         <v>89.3</v>
       </c>
       <c r="Q296" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R296">
         <v>5</v>
@@ -23165,7 +23141,7 @@
     </row>
     <row r="297" spans="1:20">
       <c r="A297" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B297">
         <v>37</v>
@@ -23213,7 +23189,7 @@
         <v>89.5</v>
       </c>
       <c r="Q297" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R297">
         <v>4</v>
@@ -23227,7 +23203,7 @@
     </row>
     <row r="298" spans="1:20">
       <c r="A298" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B298">
         <v>76</v>
@@ -23275,7 +23251,7 @@
         <v>89.7</v>
       </c>
       <c r="Q298" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R298">
         <v>3</v>
@@ -23289,7 +23265,7 @@
     </row>
     <row r="299" spans="1:20">
       <c r="A299" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B299">
         <v>55</v>
@@ -23337,7 +23313,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Q299" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R299">
         <v>2</v>
@@ -23351,7 +23327,7 @@
     </row>
     <row r="300" spans="1:20">
       <c r="A300" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B300">
         <v>45</v>
@@ -23399,7 +23375,7 @@
         <v>92.7</v>
       </c>
       <c r="Q300" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R300">
         <v>1</v>
@@ -23423,10 +23399,10 @@
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1" t="s">
         <v>415</v>
-      </c>
-      <c r="B1" t="s">
-        <v>416</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -23438,28 +23414,28 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G1" t="s">
         <v>417</v>
-      </c>
-      <c r="G1" t="s">
-        <v>418</v>
       </c>
       <c r="H1" t="s">
         <v>3</v>
       </c>
       <c r="I1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" t="s">
         <v>102</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>103</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>104</v>
       </c>
-      <c r="L1" t="s">
-        <v>105</v>
-      </c>
       <c r="M1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N1" t="s">
         <v>5</v>
@@ -23477,24 +23453,24 @@
         <v>11</v>
       </c>
       <c r="S1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T1" t="s">
+        <v>419</v>
+      </c>
+      <c r="U1" t="s">
+        <v>95</v>
+      </c>
+      <c r="V1" t="s">
         <v>420</v>
-      </c>
-      <c r="U1" t="s">
-        <v>96</v>
-      </c>
-      <c r="V1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C2">
         <v>1264</v>
@@ -23559,10 +23535,10 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C3">
         <v>479</v>
@@ -23627,10 +23603,10 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C4">
         <v>1413</v>
@@ -23695,10 +23671,10 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C5">
         <v>375</v>
@@ -23763,10 +23739,10 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C6">
         <v>4169</v>
@@ -23831,10 +23807,10 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C7">
         <v>344</v>
@@ -23899,10 +23875,10 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C8">
         <v>417</v>
@@ -23967,10 +23943,10 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <v>764</v>
@@ -24035,10 +24011,10 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C10">
         <v>6279</v>
@@ -24103,10 +24079,10 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C11">
         <v>6652</v>
@@ -24171,10 +24147,10 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C12">
         <v>9324</v>
@@ -24239,10 +24215,10 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C13">
         <v>627</v>
@@ -24307,10 +24283,10 @@
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="C14">
         <v>5602</v>
@@ -24375,7 +24351,7 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
         <v>433</v>
@@ -24443,7 +24419,7 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
         <v>434</v>
@@ -24511,7 +24487,7 @@
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
         <v>435</v>
@@ -24579,7 +24555,7 @@
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
         <v>436</v>
@@ -24647,7 +24623,7 @@
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
         <v>437</v>
@@ -24715,7 +24691,7 @@
     </row>
     <row r="20" spans="1:22">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
         <v>438</v>
@@ -24783,7 +24759,7 @@
     </row>
     <row r="21" spans="1:22">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
         <v>439</v>
@@ -24851,7 +24827,7 @@
     </row>
     <row r="22" spans="1:22">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>440</v>
@@ -24919,7 +24895,7 @@
     </row>
     <row r="23" spans="1:22">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
         <v>441</v>
@@ -24987,7 +24963,7 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
         <v>442</v>
@@ -25055,7 +25031,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
         <v>443</v>
@@ -25123,7 +25099,7 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
         <v>444</v>
@@ -25191,7 +25167,7 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
         <v>445</v>
@@ -25259,7 +25235,7 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
         <v>446</v>
@@ -25327,7 +25303,7 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s">
         <v>447</v>
@@ -25395,7 +25371,7 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
         <v>448</v>
@@ -25463,7 +25439,7 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
         <v>449</v>
@@ -25531,7 +25507,7 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
         <v>450</v>
@@ -25599,7 +25575,7 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
         <v>451</v>
